--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -38,13 +38,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'⑥ 架構抉擇'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'⑦ 術語白話對照'!$A$4:$C$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'⑦ 術語白話對照'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'⑧ 完整模組清單'!$A$4:$L$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'⑧ 完整模組清單'!$A$4:$N$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'⑧ 完整模組清單'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'⑨ ADR 決策表'!$A$4:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'⑨ ADR 決策表'!$A$4:$F$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'⑨ ADR 決策表'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'⑩ 契約與追溯風險'!$A$4:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'⑩ 契約與追溯風險'!$A$4:$F$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'⑩ 契約與追溯風險'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'元件標籤字典'!$A$4:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'元件標籤字典'!$A$4:$I$105</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'元件標籤字典'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>✅ FR 65/65 主鍵唯一；舊追溯鍵 46 個；既有 TC 90 筆。</t>
+          <t>✅ FR 65/65 主鍵唯一；舊追溯鍵 46 個；既有 TC 97 筆。</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -940,7 +940,9 @@
     <col width="72" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="78" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1015,6 +1017,16 @@
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
+          <t>Code reality</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>實作證據路徑</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
           <t>BOM 對齊</t>
         </is>
       </c>
@@ -1054,20 +1066,30 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K5" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1108,20 +1130,30 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+        </is>
+      </c>
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1162,20 +1194,30 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1221,15 +1263,25 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/</t>
+        </is>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1270,20 +1322,30 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1324,20 +1386,30 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K10" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
+        </is>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1378,20 +1450,30 @@
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1437,15 +1519,25 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（跨系統事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py</t>
+        </is>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1486,20 +1578,30 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1540,20 +1642,30 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
+        </is>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1599,15 +1711,25 @@
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1648,20 +1770,30 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1707,15 +1839,25 @@
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1756,20 +1898,30 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/}</t>
+        </is>
+      </c>
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1815,15 +1967,25 @@
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1864,20 +2026,30 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="K20" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
+        </is>
+      </c>
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1923,15 +2095,25 @@
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -1977,15 +2159,25 @@
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="K22" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
+        </is>
+      </c>
+      <c r="N22" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2031,15 +2223,25 @@
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2085,15 +2287,25 @@
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K24" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（服務已實作，部署流程未完整）</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
+        </is>
+      </c>
+      <c r="N24" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2134,20 +2346,30 @@
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
+        </is>
+      </c>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2188,20 +2410,30 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>Publisher; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
+          <t>Publisher; behavior patch artifact; LiveSkill DB ingest; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
+        </is>
+      </c>
+      <c r="N26" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2242,20 +2474,30 @@
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+      <c r="N27" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2296,20 +2538,30 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+      <c r="N28" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2350,20 +2602,30 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>事件層; 技師工單 read-model; WebSocket 端點</t>
+          <t>事件層; EventConsumerWorker; technician_workorder_projection; 技師工單 read-model; WebSocket 端點</t>
         </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2404,20 +2666,30 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>commission_settlement_service; 技師工單 read-model; Kafka</t>
+          <t>technician settlement services; technician_commission_projection; EventConsumerWorker; Kafka</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="K30" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2458,20 +2730,30 @@
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2517,15 +2799,25 @@
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="K32" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
+          <t>15_SDS §6.1、§6.3、§11</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka opt-in）</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile）</t>
+        </is>
+      </c>
+      <c r="N32" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2571,15 +2863,25 @@
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
+          <t>15_SDS §2.2、§5.1、§13</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+        </is>
+      </c>
+      <c r="N33" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2620,20 +2922,30 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>SigNoz; OPIK; OpenTelemetry</t>
+          <t>SigNoz; OPIK; OpenTelemetry; PIIScrubSpanProcessor</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="K34" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2679,15 +2991,25 @@
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+      <c r="N35" s="13" t="inlineStr">
         <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
@@ -2728,32 +3050,42 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
           <t>✅ 與 BOM L2 對齊</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L36"/>
+  <autoFilter ref="A4:N36"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:L36">
+  <conditionalFormatting sqref="A5:N36">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("🔴",A5))</formula>
     </cfRule>
@@ -2841,7 +3173,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3922,13 +4254,45 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>ADR-033</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>轉真人判準——SOP 情境式不可違反條件取代 FR-AGT-03 三輪硬計數（正典讓步；釐清檢核降為回覆內容原則；transfer 唯一出口不變）</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>系統(agent)</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>025 · 008 · 032</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F36"/>
+  <autoFilter ref="A4:F37"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F36">
+  <conditionalFormatting sqref="A5:F37">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("🔴",A5))</formula>
     </cfRule>
@@ -3950,7 +4314,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4217,7 +4581,7 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>90 筆詳細 TC 的舊 FR/來源欄不再承擔現行追溯</t>
+          <t>97 筆詳細 TC 的舊 FR/來源欄不再承擔現行追溯</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -4266,42 +4630,138 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
+          <t>實作</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>IM-02</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>technician-platform 是獨立部署 stack，但後端共用 api codebase</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>若仍寫成待確認的獨立 codebase，SAD/SDS 與程式無法對回</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Current 標 API_SURFACE=tech + lock_tech；Target OHS 邊界另列 To-Be</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5 / 15_SDS §7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>契約</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>CT-04</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>consents:send-link 已進 runtime router/generated types，但 static OpenAPI SSOT 未補登</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>靜態契約、SDK 與 runtime 可能漂移</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>補登 api/openapi.yaml 與 16_API_Spec，跑 schema diff 後才可關閉</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/work_orders_v2.py / 16_API_Spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>DP-01</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Redis/Kafka/RAG/OIDC/Refinery/Observability 多項為 code-present 或 opt-in</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>檔案存在會被誤判為 production 已啟用</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Code reality 用 PARTIAL；以部署 env、migration、SIT 與 dashboard 證據升級狀態</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Codebase現況掃描_2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
           <t>驗收</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>QA-01</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>部分 SRS/NFR 仍含 [待確認] 量化門檻</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>測試可執行但無法客觀判定 pass/fail</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>由 PM/Architect 在 UAT 前將門檻、量測點、資料集與負責人定版</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>04_SRS / 05_NFR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F13"/>
+  <autoFilter ref="A4:F16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F13">
+  <conditionalFormatting sqref="A5:F16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("🔴",A5))</formula>
     </cfRule>
@@ -4323,7 +4783,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4331,9 +4791,10 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="68" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -4378,17 +4839,22 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
+          <t>Code reality</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
           <t>SAD 定位</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>SDS 定位</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>能力群相關實作路徑 / 規劃狀態</t>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>實作證據路徑</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4871,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派訊息/事件，並將回覆送回 LINE。</t>
+          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派文字/照片/postback，並將文字與核准圖片回覆送回 LINE。</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -4418,17 +4884,22 @@
           <t>AGT·CHN</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149</t>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
@@ -4437,217 +4908,242 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>AgentLoop</t>
+          <t>Photo Guide resolver</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>LockCore runtime（產品層）</t>
+          <t>品牌照片樣本圖解析器</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
+          <t>解析 AI 回覆文末的 photo-guide 標記、剝除內部標記並按設定附加 LINE ImageMessage；目前只核准 Chatlock 安裝前樣本圖。</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
+          <t>只呈現預先核准的品牌靜態圖片；不讀取或辨識客戶照片，也不允許未設定品牌自行附圖。</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149 ｜ 12_SAD §4.1 L145–148</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374 ｜ 15_SDS §5.1 L367–374; §5.3</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>AgentRunner</t>
+          <t>Quote postback message mapper</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>LockCore runtime（通用執行層）</t>
+          <t>報價回覆錯誤回覆內容分類器</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
+          <t>依 QUOTE_EXPIRED、QUOTE_ALREADY_DECIDED、NOT_FOUND、FORBIDDEN 等 API error_code 產生對客戶可理解的 LINE 回覆。</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
+          <t>只映射終態與錯誤回覆內容；報價狀態機、權限與冪等仍由品牌 API 執行。</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149 ｜ 12_SAD §4.1 L145–148 ｜ 12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374 ｜ 15_SDS §5.1 L367–374; §5.3 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>ContextBuilder</t>
+          <t>WebhookIdempotencyStore</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>LockCore runtime（上下文層）</t>
+          <t>LINE webhook 冪等保留庫</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
+          <t>在處理 LINE event 前以 mark-first 方式保留 event ID，重送時直接略過，避免重複回覆或建卡。</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
+          <t>只治理 webhook 重播；不代替報價、工單與金流 mutation 的 Idempotency-Key。</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>LiteLLMProvider + FallbackProvider</t>
+          <t>AgentLoop</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（產品層）</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
+          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>處理模型呼叫、重試與備援切換；不承載業務規則或產品決策。</t>
+          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>AGT·GOV、PLT·LLM</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407 ｜ 12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>AGT·CHN、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Model Orchestration Layer</t>
+          <t>AgentRunner</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（通用執行層）</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>供應商無關的模型編排層：集中管理路由、備援處理、逾時、快取與呼叫效率。</t>
+          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
+          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>PLT·LLM</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>ToolRegistry</t>
+          <t>ReplyGuard</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -4657,207 +5153,232 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Agent 工具登錄與允許清單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
+          <t>Agent 回覆出口守衛：攔截確定金額、錯誤型號、假稱已轉真人等違規輸出，必要時重生或轉人工。</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
+          <t>是模型輸出的最後安全層；不取代 API 的報價、派工與權限硬閘。</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148 ｜ 12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>MemoryManager + Store</t>
+          <t>SentimentClassifier</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id。</t>
+          <t>在不阻斷主回覆的前提下判定負面情緒並產生警示所需資料。</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
+          <t>只做情緒分類與旁路警示；不單獨決定報價、派工或工單狀態。</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EscalationStore</t>
+          <t>ContextBuilder</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（上下文層）</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
+          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>保證轉人事件不遺漏；不是正式工單庫，也不代替 API 的開單 gate。</t>
+          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>AGT·RES</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>SkillsLoader + 2 builtin skills</t>
+          <t>LiteLLMProvider + FallbackProvider</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與不可違反條件。</t>
+          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
+          <t>處理模型呼叫、重試與備援切換；不承載業務規則或產品決策。</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407 ｜ 12_SAD §4.1 L147–149 ｜ 12_SAD §4.4 L183–187</t>
+          <t>AGT·GOV、PLT·LLM</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374 ｜ 15_SDS §5.1 L369–374; §5.4 ｜ 15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/</t>
+          <t>12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.2、§5.1、§13 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>記憶 DB</t>
+          <t>Model Orchestration Layer</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Memory backend</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
+          <t>供應商無關的模型編排層：集中管理路由、備援處理、逾時、快取與呼叫效率。</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
+          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>PLT·LLM</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §2.2、§5.1、§13</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>tenant-scoped routers</t>
+          <t>ToolRegistry</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4867,81 +5388,91 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
+          <t>Agent 工具登錄與允許清單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
+          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>API·CASE</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>AGT·GOV、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>api/routers/; api/services/; api/core/db.py</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（problem_card / quote）</t>
+          <t>MemoryManager + Store</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
+          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id；預設 SQLite，可設定 PostgreSQL。</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
+          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>API·CASE</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>api/routers/; api/services/; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）</t>
+          <t>EscalationStore</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -4951,81 +5482,91 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
+          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>不允許 AI 繞過客戶確認與人工審核直接轉工單。</t>
+          <t>保證轉人事件不遺漏；不是正式工單庫，也不代替 API 的開單 gate。</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>API·WO</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）</t>
+          <t>SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
+          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與不可違反條件。</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
+          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>API·DISP</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9 ｜ 12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1 ｜ 15_SDS §5.1、§5.4 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Service Layer（invoice / settlement）</t>
+          <t>SkillSync</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -5035,81 +5576,91 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
+          <t>輪詢品牌庫已發布的 skill revision，以原子交換同步到 workspace overlay，讓新版本在執行期生效。</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
+          <t>只同步已發布版本且失敗時保留舊版；不自行核准 draft，也不覆寫平台保護層。</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>API·FIN</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>api/services/{invoice,settlement}*; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>core/db.py</t>
+          <t>記憶 DB</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory backend</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>API 資料庫基礎層：管理連線池、交易邊界與讀寫分離。</t>
+          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>不放領域流程決策；業務交易應由 service 層呼叫。</t>
+          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §4.2 L151–164; §9 L401 ｜ 12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466 ｜ 15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472 ｜ 15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql ｜ api/routers/; api/services/; api/core/db.py ｜ api/services/work_order_service.py; api/routers/; api/core/db.py ｜ api/services/{invoice,settlement}*; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>internal_ingest.py</t>
+          <t>tenant-scoped routers</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -5119,39 +5670,44 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
+          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>只接受驗證失敗即拒絕內部憑證；不是 LINE webhook 入站門。</t>
+          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>API·INT</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service*</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>WebSocket 端點</t>
+          <t>Service Layer（problem_card / quote）</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -5161,81 +5717,91 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
+          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
+          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394 ｜ 12_SAD §4.5 L189–197 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548 ｜ 15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677 ｜ 15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Redis pub/sub</t>
+          <t>Conversation media collector</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>對話照片掛卡器</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
+          <t>AI 建問題卡時反查同一對話近 24 小時內最多 5 張照片，依時間排序附加到 media_urls。</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
+          <t>只掛接已持久化媒體 URL，採 append-only 且查詢失敗略過；不做任何影像辨識。</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>API·DISP、API·INT、PLT·EVT</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Service Layer（work_order）</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -5245,81 +5811,91 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>持久、可重播的跨系統事件骨幹，傳遞 technician.*、dispatch.*、workorder.* 與 commission.* 等事件。</t>
+          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
+          <t>不允許 AI 繞過客戶確認與人工審核直接轉工單。</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L151–164; §9 L401 ｜ 12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394 ｜ 12_SAD §4.5 L189–197; §9 L401</t>
+          <t>API·WO</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560 ｜ 15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677 ｜ 15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677 ｜ 15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ api/services/dispatch*; api/realtime/; Kafka integration ｜ api/services/{invoice,settlement}*; api/core/db.py ｜ knowledge-pipeline/; api/realtime/; Kafka integration ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>分散式排程</t>
+          <t>Consent link service</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免責同意簽署連結服務</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>跨實例協調 SLA、GDPR 永久刪除、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
+          <t>為工單產生公開簽署 token、保存 token hash 稽核並透過 LINE 推送；無 LINE 綁定時回傳可複製連結。</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
+          <t>只負責交付簽署入口與稽核；簽署內容、角色/租戶授權與結案 gate 仍由 API 驗證。</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>API·DISP、PLT·EVT</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>API·WO</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>line_push_service + outbox worker</t>
+          <t>Service Layer（dispatch）</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -5329,81 +5905,91 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
+          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>推播失敗不還原主業務寫入；不處理 LINE 入站 webhook。</t>
+          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>API·INT</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>API·DISP</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service*</t>
+          <t>12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>守衛鏈</t>
+          <t>dispatch_service candidate scoring</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>現行媒合評分器</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
+          <t>現行派工服務直接由技師權威資料評估技能、品牌授權、距離、評分、工作量與公平性，產生候選排序。</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>逐端點預設拒絕 enforce；不把前端隱藏按鈕當成安全控制。</t>
+          <t>這是共用 API codebase 的 interim 實作；目標 OHS/MatchingService 獨立服務邊界尚未拆出。</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>API·GOV、PLT·IAM、TEC·ID</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393 ｜ 12_SAD §4.5 L189–197 ｜ 12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>API·DISP、TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670 ｜ 15_SDS §6.1 L428–472; §6.4 L494–499 ｜ 15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認） ｜ web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/ ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>core/errors.py</t>
+          <t>Service Layer（invoice / settlement）</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -5413,39 +5999,44 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
+          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
+          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·FIN</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>core/idempotency.py</t>
+          <t>core/db.py</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -5455,123 +6046,138 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
+          <t>API 資料庫基礎層：管理品牌庫、技師權威庫與平台庫的連線取得、交易邊界及安全備援處理。</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
+          <t>不放領域流程決策；業務交易應由 service 層呼叫。</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6 ｜ 12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1 ｜ 15_SDS §4.2、§4.6、§6.1 ｜ 15_SDS §4.2、§6.1、§7.3</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Middleware</t>
+          <t>API_SURFACE router filter</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>API 部署面塑形器</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
+          <t>同一 FastAPI codebase 依 API_SURFACE=dispatch/tech/platform 裁切路由與背景 worker，形成三個可獨立部署面。</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>不承載單一領域的核心業務規則。</t>
+          <t>只縮小部署暴露面，不是授權邊界；每個保留端點仍須 RBAC、租戶或平台守衛。</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·GOV、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>AuthGuard</t>
+          <t>Three-DB Connection Router</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫連線路由</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
+          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
+          <t>治理資料庫選擇與驗證失敗即拒絕；不代表 production migration 或 backfill 已完成。</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>appMode gate</t>
+          <t>DBPoolScopeMiddleware</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -5581,81 +6187,91 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
+          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
+          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>rolePolicy</t>
+          <t>DEKService + PII blind index + purge ledger</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>個資密鑰與清除稽核套件</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
+          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>只提供前端 UX 治理；不代替 API role_required。</t>
+          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599 ｜ 15_SDS §8.1 L570–578</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts ｜ web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>api client</t>
+          <t>internal_ingest.py</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
@@ -5665,39 +6281,44 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
+          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
+          <t>只接受驗證失敗即拒絕內部憑證；不是 LINE webhook 入站門。</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578 ｜ 15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts ｜ web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>cache</t>
+          <t>WebSocket 端點</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -5707,39 +6328,44 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
+          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
+          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>realtime</t>
+          <t>Redis pub/sub</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
@@ -5749,39 +6375,44 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
+          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>負責前端即時連線生命週期；不是事件持久層。</t>
+          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·DISP、API·INT、PLT·EVT</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>型別（api.generated.ts）</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -5791,39 +6422,44 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
+          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
+          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>WEB·AUD</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Medallion pipeline</t>
+          <t>EventBusProducer</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
@@ -5833,39 +6469,44 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
+          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
+          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>source_to_raw</t>
+          <t>EventConsumerWorker</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -5875,39 +6516,44 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>收集原始外部素材並原樣實作到 raw 層，保留來源識別與取得資訊。</t>
+          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
+          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>TEC·PROJ、TEC·SET</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>raw_to_bronze</t>
+          <t>分散式排程</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
@@ -5917,39 +6563,44 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
+          <t>跨實例協調 SLA、GDPR 永久刪除、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
+          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187 ｜ 12_SAD §4.6 L199–208</t>
+          <t>API·DISP、PLT·EVT</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635 ｜ 15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>bronze_to_silver</t>
+          <t>PG Advisory Cron Leader</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -5959,39 +6610,44 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
+          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>silver 不等於已核可發布；下游仍需提煉、人工審核與 Publisher gate。</t>
+          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187 ｜ 12_SAD §4.6 L199–208</t>
+          <t>API·DISP</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G42" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635 ｜ 15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>storage（raw/bronze/silver）</t>
+          <t>line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -6001,39 +6657,44 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
+          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
+          <t>推播失敗不還原主業務寫入；不處理 LINE 入站 webhook。</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql</t>
+          <t>守衛鏈</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -6043,39 +6704,44 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
+          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
+          <t>逐端點預設拒絕 enforce；不把前端隱藏按鈕當成安全控制。</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV、PLT·IAM、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>forward-only migrations</t>
+          <t>core/errors.py</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -6085,39 +6751,44 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
+          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
+          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>platform schema</t>
+          <t>core/idempotency.py</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -6127,39 +6798,44 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
+          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>不存單一品牌內的工單、客戶或報價真相。</t>
+          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>MCP RAG server</t>
+          <t>Middleware</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -6169,39 +6845,44 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
+          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
+          <t>不承載單一領域的核心業務規則。</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>品牌庫 pgvector</t>
+          <t>AuthGuard</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -6211,39 +6892,44 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
+          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
+          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>DAT·RAG、REF·PUB</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187 ｜ 12_SAD §8.1 L353–361; §9 L407</t>
+          <t>WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677 ｜ 15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/ ｜ rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>rag_manual_chunks / case_entries</t>
+          <t>appMode gate</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
@@ -6253,39 +6939,44 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
+          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
+          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>outbox</t>
+          <t>rolePolicy</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -6295,39 +6986,44 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
+          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件紀錄。</t>
+          <t>只提供前端 UX 治理；不代替 API role_required。</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>WEB·AUD、WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>provenance / audit</t>
+          <t>api client</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
@@ -6337,123 +7033,138 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
+          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>不允許 LLM 自行編造來源，也不把一般顯示紀錄當成不可否認稽核鏈。</t>
+          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>汲取層</t>
+          <t>AuthImage / AuthImageLightbox</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>需認證媒體縮圖與預覽</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
+          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
+          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>提煉分流器</t>
+          <t>ConsentPanel</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>工單免責同意面板</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
+          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>只產生 draft；未經人工審核核可不得寫入 pgvector 或 Skill。</t>
+          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>REF·REFINE</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Draft Queue</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -6463,39 +7174,44 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
+          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>是待審產物，不是已發布知識。</t>
+          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>REF·人工審核、REF·REFINE</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635 ｜ 15_SDS §9.1 L615–616; §9.2 L621–629</t>
-        </is>
-      </c>
-      <c r="H54" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>審核 UI backend</t>
+          <t>realtime</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
@@ -6505,39 +7221,44 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的人工審核後端。</t>
+          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
+          <t>負責前端即時連線生命週期；不是事件持久層。</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>REF·人工審核</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
-        </is>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>型別（api.generated.ts）</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -6547,39 +7268,44 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/產出檔。</t>
+          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人工審核 gate。</t>
+          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·AUD</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>self-service routers</t>
+          <t>Medallion pipeline</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
@@ -6589,39 +7315,44 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>technician_service</t>
+          <t>source_to_raw</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -6631,39 +7362,44 @@
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+          <t>收集原始外部素材並原樣實作到 raw 層，保留來源識別與取得資訊。</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>certification/kyc_service</t>
+          <t>raw_to_bronze</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
@@ -6673,39 +7409,44 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>未核可或已失效認證不得進入媒合候選集。</t>
+          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED、REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>lock_tech</t>
+          <t>bronze_to_silver</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -6715,39 +7456,44 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+          <t>silver 不等於已核可發布；下游仍需提煉、人工審核與 Publisher gate。</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED、REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>OHS API routers</t>
+          <t>storage（raw/bronze/silver）</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
@@ -6757,39 +7503,44 @@
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G61" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>matching_service</t>
+          <t>SQL/Schema*.sql</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -6799,39 +7550,44 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>依技能、地區、品牌授權、認證、可用性、評分與工作量排序技師候選。</t>
+          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>回傳候選不等於已指派；不繞過 active、授權與認證 gate。</t>
+          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H62" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>schedule_service</t>
+          <t>forward-only migrations</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
@@ -6841,39 +7597,44 @@
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H63" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>事件層</t>
+          <t>platform schema</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -6883,39 +7644,44 @@
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+          <t>不存單一品牌內的工單、客戶或報價真相。</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>TEC·MATCH、TEC·PROJ</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548 ｜ 15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>技師工單 read-model</t>
+          <t>MCP RAG server</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
@@ -6925,39 +7691,44 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌完整敏感資料。</t>
+          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>TEC·PROJ、TEC·SET</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197; §9 L401 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>DAT·RAG</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660 ｜ 15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H65" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>commission_settlement_service</t>
+          <t>品牌庫 pgvector</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -6967,39 +7738,44 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>匯總各品牌 commission.accrued，建立技師跨品牌 statement、payout 與期末對帳。</t>
+          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>不重算品牌工單的 Billing 明細；差異以 reconcile gate 收斂。</t>
+          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>DAT·RAG、REF·PUB</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Casdoor</t>
+          <t>rag_manual_chunks / case_entries</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
@@ -7009,39 +7785,44 @@
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>發行身分與角色資訊；資源層授權仍由各 API 預設拒絕 enforce。</t>
+          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F67" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·RAG</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G67" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
+        </is>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>平台維運 console</t>
+          <t>outbox</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -7051,39 +7832,44 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件紀錄。</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>License provisioning</t>
+          <t>provenance / audit</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
@@ -7093,39 +7879,44 @@
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+          <t>不允許 LLM 自行編造來源，也不把一般顯示紀錄當成不可否認稽核鏈。</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G69" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H69" s="13" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>SigNoz</t>
+          <t>汲取層</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -7135,39 +7926,44 @@
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與警示。</t>
+          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H70" s="14" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>OPIK</t>
+          <t>提煉分流器</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
@@ -7177,39 +7973,44 @@
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>專注 AI 呼叫品質；不代替 SigNoz 的全系統可觀測性。</t>
+          <t>只產生 draft；未經人工審核核可不得寫入 pgvector 或 Skill。</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·REFINE</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（服務已實作，部署流程未完整）</t>
         </is>
       </c>
       <c r="G71" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>OpenTelemetry</t>
+          <t>Draft Queue</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -7219,39 +8020,44 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+          <t>是待審產物，不是已發布知識。</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·人工審核、REF·REFINE</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已實作，部署流程未完整）</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H72" s="14" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Flow DSL executor</t>
+          <t>審核 UI backend</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
@@ -7261,39 +8067,44 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的人工審核後端。</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·人工審核</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G73" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H73" s="13" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>domain blocks / primitives</t>
+          <t>Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -7303,39 +8114,44 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·人工審核</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H74" s="14" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Vertical Pack</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
@@ -7345,39 +8161,44 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>可版本化的產業設定包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/產出檔。</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人工審核 gate。</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>PLT·CFG、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H75" s="13" t="inlineStr">
-        <is>
-          <t>待 M4 實作；目前為 SDS 設計元件 ｜ 待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>FlowEditor</t>
+          <t>behavior patch artifact</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -7387,39 +8208,44 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+          <t>行為軌核可後產生 target_path + content 的受控產出檔，保存於 draft provenance，交由 apply CLI 消費。</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及人工審核 gate。</t>
+          <t>產出檔仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git 備援處理才生效。</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H76" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry</t>
+          <t>LiveSkill DB ingest</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
@@ -7429,84 +8255,1363 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央設定能力。</t>
+          <t>apply_behavior 預設呼叫 internal skills ingest，將核可產出檔以加性合併建立品牌 skill draft，再由後台人工發布。</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>租戶只可改客製層；安全、金額、工具允許清單等保護層不可 override。</t>
+          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git 備援處理。</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H77" s="13" t="inlineStr">
-        <is>
-          <t>待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="14" t="inlineStr">
         <is>
+          <t>self-service routers</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H78" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>technician_service</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>certification/kyc_service</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>未核可或已失效認證不得進入媒合候選集。</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>OHS API routers</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>schedule_service</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>事件層</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>TEC·MATCH、TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>technician_workorder_projection</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>技師工單 read-model</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌完整敏感資料。</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H86" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>technician_commission_projection</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>TEC·SET</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>technician settlement services</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已實作。</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>TEC·SET</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H88" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>Tech DB router + mirror</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>技師權威庫路由與相容鏡射</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>DAT·SCH、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>Casdoor</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>發行身分與角色資訊；資源層授權仍由各 API 預設拒絕 enforce。</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>License Entitlement Gate</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應驗證失敗即拒絕。</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>是應用層授權檢查；不等於部署 per-brand bundle 的環境開通設定自動化。</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>平台維運 console</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>License provisioning</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>SigNoz</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與警示。</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H94" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>OPIK</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>專注 AI 呼叫品質；不代替 SigNoz 的全系統可觀測性。</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G95" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>OpenTelemetry</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H96" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>PIIScrubSpanProcessor</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Flow DSL executor</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H98" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>domain blocks / primitives</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>Vertical Pack</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>可版本化的產業設定包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>PLT·CFG、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H100" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>FlowEditor</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及人工審核 gate。</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Agent Configuration Studio / Config Registry</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央設定能力。</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>租戶只可改客製層；安全、金額、工具允許清單等保護層不可 override。</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H102" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>M18 Config Registry</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>已實作的設定服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>只涵蓋現行 M18 設定能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Skill Revision Registry</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H104" s="16" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
           <t>HITL 審核骨架</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C105" s="13" t="inlineStr">
         <is>
           <t>共用的 draft→diff→人工審核→核可/駁回→發布模式，同時支援知識精煉與 AI Onboarding Compiler。</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
         <is>
           <t>AI 只產生 draft；高風險知識或流程未人工審核不得實作。</t>
         </is>
       </c>
-      <c r="E78" s="14" t="inlineStr">
+      <c r="E105" s="13" t="inlineStr">
         <is>
           <t>PLT·CFG</t>
         </is>
       </c>
-      <c r="F78" s="16" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr">
-        <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H78" s="14" t="inlineStr">
-        <is>
-          <t>待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G105" s="15" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H78"/>
+  <autoFilter ref="A4:I105"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H78">
+  <conditionalFormatting sqref="A5:I105">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("🔴",A5))</formula>
     </cfRule>
@@ -7518,154 +9623,208 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -8338,7 +10497,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：當客戶傳送文字或照片時，合法訊息會進入客服流程並收到回覆；無效來源被拒絕，系統異常時仍有友善說明。 ｜ 成功指標：每則訊息必有回覆（含錯誤時友善回覆內容）；單則 ≤ 4900 字截斷</t>
+          <t>PRD 驗收：當客戶傳送文字或照片時，合法訊息會進入客服流程並收到回覆；Chatlock 安裝前拍照引導可附核准樣本圖，其他品牌維持純文字；無效來源被拒絕，系統異常時仍有友善說明。 ｜ 成功指標：每則訊息必有回覆（含錯誤時友善回覆內容）；單則 ≤ 4900 字截斷</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -8422,7 +10581,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：當問題卡資訊完整時，客戶會先收到相符的解決建議並被詢問是否已釐清；連續三次未釐清時自動轉人工。 ｜ 成功指標：已釐清寫 clarification_confirmed_at；連續 3 次未釐清升級轉真人</t>
+          <t>PRD 驗收：當問題資訊不足時，系統依當下情境一次列齊必要問題；客戶明確要求真人、急迫派工、涉及金錢或連續兩次表達不滿時立即轉人工，不採固定追問輪數。 ｜ 成功指標：已釐清寫 clarification_confirmed_at；連續 3 次未釐清升級轉真人</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -8800,7 +10959,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>PRD 驗收：AI 可草擬問題卡，客服能補齊與確認；未達完整度或未經客服確認時，不得自動轉成工單。 ｜ 成功指標：AI 不得自行建立工單；confirm/convert 走客服認證端點</t>
+          <t>PRD 驗收：AI 可草擬問題卡，並將同一對話近 24 小時內最多 5 張客戶照片附上供客服檢視；客服能補齊與確認，未達完整度或未經客服確認時不得自動轉成工單。 ｜ 成功指標：AI 不得自行建立工單；confirm/convert 走客服認證端點</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -8842,7 +11001,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：報價必須依序完成內部核准、客戶送達與客戶確認；保固或專案報價不得由 AI 直接送出，客戶畫面不顯示成本欄位。 ｜ 成功指標：sender_role=ai_agent AND case_type∈{warranty,project} → 403 AI_FORBIDDEN_WARRANTY_PROJECT；quote 內外雙視圖（客戶端不含成本欄）</t>
+          <t>PRD 驗收：報價必須依序完成內部核准、客戶送達與客戶確認；重複同一決定安全回放，相反決定、過期、無權或找不到報價時顯示對應說明；保固或專案報價不得由 AI 直接送出，客戶畫面不顯示成本欄位。 ｜ 成功指標：sender_role=ai_agent AND case_type∈{warranty,project} → 403 AI_FORBIDDEN_WARRANTY_PROJECT；quote 內外雙視圖（客戶端不含成本欄）</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -8926,7 +11085,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：報價已獲客戶確認或符合急件例外時，客服可一次操作建立工單；重複送出不產生第二張工單，並留下建單來源。 ｜ 成功指標：create_trigger 記錄 AI/CS 路徑；idempotency_key 防重</t>
+          <t>PRD 驗收：報價已獲客戶確認或符合急件例外時，客服可一次操作建立工單；問題卡中的客戶姓名、電話、地址、品牌、型號與序號會帶入工單，重複送出不產生第二張工單並留下建單來源。 ｜ 成功指標：create_trigger 記錄 AI/CS 路徑；idempotency_key 防重</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -9094,7 +11253,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：技師可上傳到場與施工證據、登錄受控材料並取得客戶簽名；證據不齊或現場範圍變更未完成必要確認時不得結案。 ｜ 成功指標：結案前證據齊備檢核；scope change 走 §2.2.5 分層</t>
+          <t>PRD 驗收：技師可上傳到場與施工證據、登錄受控材料；客服可將三段免責簽署連結推送到 LINE，未綁 LINE 時可複製連結交付；證據、簽署或現場範圍變更確認不齊時不得結案。 ｜ 成功指標：結案前證據齊備檢核；scope change 走 §2.2.5 分層</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -9682,7 +11841,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：派工人員可查看工單看板、待派佇列與即時更新；即時連線中斷時畫面不崩潰，仍可查詢與完成核心作業。 ｜ 成功指標：即時降級 100% 不當機</t>
+          <t>PRD 驗收：派工人員可查看工單看板、待派佇列、技師全名與需授權照片的縮圖/放大檢視；即時連線中斷或照片載入失敗時畫面不崩潰，仍可查詢與完成核心作業。 ｜ 成功指標：即時降級 100% 不當機</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -9808,7 +11967,7 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>PRD 驗收：客戶可查看報價明細、分層閱讀條款、勾選同意並追蹤工單進度；簡化備援方式也會準確記錄客戶同意來源。 ｜ 成功指標：customer_consent_method 區分 liff_full / flex_simple_fallback</t>
+          <t>PRD 驗收：客戶可由 LINE 或備援連結查看報價與三段免責條款、勾選同意並追蹤工單進度；公開 token 僅保存雜湊稽核，畫面遮蔽不必要個資。 ｜ 成功指標：customer_consent_method 區分 liff_full / flex_simple_fallback</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -9850,7 +12009,7 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>PRD 驗收：任一主要 API、網路或頁面錯誤都顯示可理解的狀態、影響與下一步建議；錯誤不導致整個應用程式崩潰。 ｜ 成功指標：任何 API 失敗有友善 UI</t>
+          <t>PRD 驗收：任一主要 API、網路、頁面或需認證媒體載入錯誤都顯示可理解的狀態、影響與下一步建議；錯誤不導致整個應用程式崩潰。 ｜ 成功指標：任何 API 失敗有友善 UI</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -11798,7 +13957,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>🔶 code 面 ✅（CR-0136 api＋CR-0156 agent/refinery/web-參考實作＋agent OPIK 接線＋PII scrub 全面，2026-07-10）；殘＝SigNoz 叢集部署與 OPIK/OTLP secrets 設定（OPS）＋三站複製</t>
+          <t>🔶 code 面 ✅（CR-0136 api＋CR-0156 agent/refinery/web-參考實作＋agent OPIK 接線＋PII scrub 全面，2026-07-10）；殘＝SigNoz 叢集部署與 OPIK/OTLP secrets 設定（OPS）＋三站複製〔標註 2026-07-22：三站複製完成——tech-portal/landing/platform-console 各補 instrumentation.ts（OTLP opt-in no-op 範式同 brand-portal）＋@vercel/otel＋vitest 單元測試 6×3 綠（feat/otel-three-portals）；code 面殘項歸零，僅剩 SigNoz 部署＋secrets 設定（純 OPS）〕〔標註 2026-07-22（業主決議）：維持 🔶／In Progress，SigNoz 部署綁「真實營運開始」——SigNoz 為常駐基礎設施（ClickHouse ~$50-100/月+維運），非一次性設定；單品牌尚無真實流量，現在部署無資料可看。解除條件＝營運流量開始後部署 SigNoz 叢集+設 OTEL_EXPORTER_OTLP_ENDPOINT。In Progress 誠實反映「code 完成、後端未部署」，非停滯。全 In Progress 解除條件盤點＝docs/audit/inprogress-exit-criteria-20260722.md〕</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -11926,7 +14085,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅ 2026-07-22（業主決議完成判準改制：功能完成＋代理 UAT＝完成，親驗移交外部測試人員。收案依據：三輪代理 UAT 112 findings 全數收斂＋合約不可違反條件 eval 實測 K8 98.5%/K3' 100%/不可違反條件 9/9＋0719 上雲 C 系列修復輪。外部驗證依 UAT-M1M2-acceptance-檢查清單，發現以新 finding 開卡不重開 gate）</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -12182,7 +14341,7 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>🔶 方案A/B 已實作（CR-0112：雙 stack＋技師身分權威庫拆分＋投影雙寫＋API_SURFACE 塑形＋tech web；稽核 2026-07-10 確認）。ADR-016 完整形式（OHS API/事件投影/品牌不直連）依業主 0703 決議隨 AI-2/AI-3</t>
+          <t>🔶 方案A/B 已實作（CR-0112：雙 stack＋技師身分權威庫拆分＋投影雙寫＋API_SURFACE 塑形＋tech web；稽核 2026-07-10 確認）。ADR-016 完整形式（OHS API/事件投影/品牌不直連）依業主 0703 決議隨 AI-2/AI-3〔標註 2026-07-22（Plane 對帳輪）：Plane 卡已改 Done——0719 tech/platform 上雲＋B1 業主親證（0721 codegraph 稽核輪改卡）；殘項 ADR-016 完整形式本屬階段二 AI-2/AI-3 範圍，階段一範圍已完。原文 🔶 不動，狀態升 ✅ 留待業主確認〕</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -12342,7 +14501,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>🔶 SIT ✅ 2026-07-10（CR-0147：api 1738＋agent 162＋rag 7（含新 MCP 整合）＋refinery 12 全部通過；五項 live 實際驗證含 refinery 真 LLM 煉製與 OIDC 瀏覽器全流程）。UAT=業主（M1 1.7.2＋M2 驗收，合約不可違反條件 K1/K3/K8）〔標註 2026-07-18：功能面 UAT 前置已由兩輪大範圍代理 UAT 收斂——業主指示代理實測（第一輪 5 角色四站 39 findings＋第二輪六功能域 43 findings，共 82 項）→ 修復/決議全數處置（api 全套 1931 綠、四站 tsc 0；報告 docs/uat/uat-full-report-20260718.md＋uat-round2-report-20260718.md）。本列 UAT gate 本體（業主親驗＋合約不可違反條件 K1/K3/K8 live）仍待業主執行，不因代理 UAT 視為通過〕</t>
+          <t>🔶 SIT ✅ 2026-07-10（CR-0147：api 1738＋agent 162＋rag 7（含新 MCP 整合）＋refinery 12 全部通過；五項 live 實際驗證含 refinery 真 LLM 煉製與 OIDC 瀏覽器全流程）。UAT=業主（M1 1.7.2＋M2 驗收，合約不可違反條件 K1/K3/K8）〔標註 2026-07-18：功能面 UAT 前置已由兩輪大範圍代理 UAT 收斂——業主指示代理實測（第一輪 5 角色四站 39 findings＋第二輪六功能域 43 findings，共 82 項）→ 修復/決議全數處置（api 全套 1931 綠、四站 tsc 0；報告 docs/uat/uat-full-report-20260718.md＋uat-round2-report-20260718.md）。本列 UAT gate 本體（業主親驗＋合約不可違反條件 K1/K3/K8 live）仍待業主執行，不因代理 UAT 視為通過〕〔標註 2026-07-22：✅ 收案——業主決議完成判準改制（功能完成＋代理 UAT＝完成，親驗移交外部測試人員）；收案依據＝SIT 全部通過＋三輪代理 UAT 112 findings＋雲端 B1/B2 實際驗證；LiveSkill 親驗版一併移交外部測試。前段 0718 標註之「不因代理 UAT 視為通過」自此依新判準失效〕</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -12374,7 +14533,7 @@
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⬜〔標註 2026-07-22（Plane 對帳輪）：Plane 卡=In Progress——0721 codegraph 稽核證事件骨幹 code 已在，惟 opt-in KAFKA_BOOTSTRAP 未啟用=runtime 休眠；非未動工亦非完成〕</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -12438,7 +14597,7 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⬜〔標註 2026-07-22（Plane 對帳輪）：Plane 卡=In Progress——0721 codegraph 稽核證 reconcile 閘門雛形 code 已在，生產未啟用〕</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -12502,7 +14661,7 @@
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⬜〔標註 2026-07-22（Plane 對帳輪）：Plane 卡=Done——0719 tech/platform 面雲端部署＋技師庫上雲，B1 業主親證（0721 稽核輪改卡）；本列經業主確認後可打 ✅〕</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>🔶 drift-check ✅ 2026-07-09（CR-0136：migration 檔案層守門 CI＋12 支波次補登；Cloud Run CD 觸發器＝OPS）</t>
+          <t>🔶 drift-check ✅ 2026-07-09（CR-0136：migration 檔案層守門 CI＋12 支波次補登；Cloud Run CD 觸發器＝OPS）〔標注 2026-07-27：再增兩道 CI gate——①web-lint-typecheck.yml（四站 matrix tsc+eslint；補前發現四站 npm run lint 因無 ESLint 設定與依賴而從未運作過）②scripts/ci/endpoint-guard-audit.py（端點守衛不對稱雙檢：v2/legacy 孿生＋list/detail），已反向驗證有效（修復前抓 8 組、修復後清零）〕</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-07-09（CR-0137：api 1719 passed 全綠＋修 seed 順序 bug/測試污染/legacy 斷言；1 live 測試 Vertex 429 非迴歸）</t>
+          <t>✅ 2026-07-09（CR-0137：api 1719 passed 全綠＋修 seed 順序 bug/測試污染/legacy 斷言；1 live 測試 Vertex 429 非迴歸）〔標注 2026-07-27：全套回歸能力解封——新增 scripts/db/make-test-db.sh（pg_dump 複製 UAT 庫＋補套 migration 建隔離 scratch 庫），此前因 pytest 單庫 fallback 直打 5433 UAT 庫而無法安全跑全套。實測 api 2091 passed / 13 failed（13 支 seed 依賴非回歸）＋agent 309 passed；並據此確認本輪 20 個端點角色守衛變更零回歸〕</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2199,458 +2199,490 @@
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
+          <t>3.6.1</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>flow DSL 引擎產品化</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>前端 mutation contract：optimistic／server-confirmed 分級、rollback、精準 invalidation、action idempotency、409 conflict UX</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>FE+BE+QA</t>
+        </is>
+      </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>從鎖匠 pack 抽出引擎（DSL-first 鐵律：引擎先於 UI）；積木契約 + 匯入靜態驗證 / ADR-013；15_SDS §3.3-3.5</t>
+          <t>ADR-034</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
+          <t>3.6.2</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>兩層渲染</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>偏好與登入資料分層：三庫 user_preferences allowlist、跨裝置同步；localStorage token 退場</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>FE+BE+DT</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>field_metadata 配置驅動（DynamicForm/Table）+ ui_composition 元件組裝；現行鎖匠前端漸進遷移，不 big-bang 重寫 / ADR-001；07_workorder §8.1</t>
+          <t>ADR-034；2.1.1；OD-004 提供 principal/claim input</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
+          <t>3.6.3</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Vertical Pack 打包</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Brand Portal Capability-driven Command Palette v1</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>FE+BE</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>pack@version + 租戶覆寫 + 向後相容檢查；鎖匠版收斂為第一個正式 pack / 07_workorder §4</t>
+          <t>3.6.2；ADR-034</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
+          <t>3.6.4</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>積木庫 bootstrap</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>API resource ownership matrix 與 BOLA／IDOR parameterized contract tests</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>SEC+BE+QA</t>
+        </is>
+      </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>頭 2-3 產業積木手工建（誠實面對冷啟動） / ADR-014 鐵律 2</t>
+          <t>ADR-035</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
+          <t>3.6.5</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>FlowEditor 拖拉</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Service principal／credential lifecycle：hash、scope、expiry、rotation、revoke、audit；遷移共用 X-Internal-Token</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Platform+SEC+BE</t>
+        </is>
+      </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>薄編輯器，只產出/編修 DSL / FR-F07</t>
+          <t>ADR-036；OD-001／OD-004</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
+          <t>3.6.6</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AI Onboarding Compiler</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Background runtime 拆分：job registry、worker entrypoint、Cloud Scheduler/Run Job pilot、outbox metrics</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>BE+OPS</t>
+        </is>
+      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>SOP/訪談 → Block Ontology → draft DSL → HITL 人審（金流/派工/同意書必過人審）；與 knowledge-refinery 共用審核 UI 骨架 / ADR-014 / FR-F08</t>
+          <t>ADR-037；GCP IAM/Scheduler</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>3.6.7</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>GCP staging→production promotion、GitHub Environments、WIF 隔離、release manifest、rollback/restore evidence</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>OPS+QA+SEC</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>ADR-038；3.6.4；3.6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>3.6.8</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>web/shared-contract 版本化窄例外：runtime types、RFC7807、mutation/conflict、capability contract</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>FE+OPS</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>ADR-039；3.6.1；ADR-031 runtime export</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>flow DSL 引擎產品化</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>從鎖匠 pack 抽出引擎（DSL-first 鐵律：引擎先於 UI）；積木契約 + 匯入靜態驗證 / ADR-013；15_SDS §3.3-3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>兩層渲染</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>field_metadata 配置驅動（DynamicForm/Table）+ ui_composition 元件組裝；現行鎖匠前端漸進遷移，不 big-bang 重寫 / ADR-001；07_workorder §8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Vertical Pack 打包</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>pack@version + 租戶覆寫 + 向後相容檢查；鎖匠版收斂為第一個正式 pack / 07_workorder §4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>積木庫 bootstrap</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>頭 2-3 產業積木手工建（誠實面對冷啟動） / ADR-014 鐵律 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>FlowEditor 拖拉</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>薄編輯器，只產出/編修 DSL / FR-F07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>AI Onboarding Compiler</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>SOP/訪談 → Block Ontology → draft DSL → HITL 人審（金流/派工/同意書必過人審）；與 knowledge-refinery 共用審核 UI 骨架 / ADR-014 / FR-F08</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>第 2 產業落地</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>FDE 4 配置面走通（診斷 / 知識精煉 / flow / UI 組裝），驗證飛輪 / 07_workorder §8.2</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>ADR —— 14_ADR/00_INDEX.md（append-only，不改舊內容）</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>群 A — 平台奠基與部署</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>ADR-001</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>平台核心 vs 領域配置分層（TRIZ 按系統層級分離）</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>009 · 013 · 014 · 002</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>群 A — 平台奠基與部署</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>ADR-002</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>per-brand 授權部署（大單體 + 內部容器 + 集中共用元件）</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>004 · 016 · 020 · 006</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>群 A — 平台奠基與部署</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>ADR-003</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>排程中</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>平台工程治理排程（migration 防漂移・API 收斂・CD）</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>002 · 021 · 022</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>群 B — 身分與授權</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>ADR-004</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Casdoor 統一 IdP + 租戶 + License 授權</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>005 · 002 · 024</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>群 B — 身分與授權</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>ADR-005</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>四方 RBAC 模型 + enforce（deny-by-default）</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>004 · 016 · 022</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>群 C — 即時、事件與可觀測性</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>ADR-006</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>規劃中</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>即時高併發骨幹（Kafka 事件 + Redis fanout + 讀寫分離）</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>002 · 016 · 017 · 007</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>群 C — 即時、事件與可觀測性</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>ADR-007</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>可觀測性分層（SigNoz 系統監控 + OPIK Agent LLM Ops）</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>002 · 009 · 012</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>群 D — Agent 與模型</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>ADR-008</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Agent 核心採 LockCore（fork nanobot 最小核心）</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>系統(agent)</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>009 · 010 · 011 · 025</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>群 D — Agent 與模型</t>
+          <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ADR-009</t>
+          <t>ADR-001</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -2660,7 +2692,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Model Orchestration Layer 供應商無關（LiteLLM 實作）</t>
+          <t>平台核心 vs 領域配置分層（TRIZ 按系統層級分離）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -2670,7 +2702,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>001 · 008 · 010 · 007</t>
+          <t>009 · 013 · 014 · 002</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
@@ -2678,12 +2710,12 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>群 D — Agent 與模型</t>
+          <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>ADR-010</t>
+          <t>ADR-002</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -2693,17 +2725,17 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>知識分層：Skill 行為驅動 + RAG-via-MCP 檢索（從屬非收斂）</t>
+          <t>per-brand 授權部署（大單體 + 內部容器 + 集中共用元件）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>系統(agent)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>008 · 011 · 018 · 019 · 012</t>
+          <t>004 · 016 · 020 · 006</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
@@ -2711,32 +2743,32 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>群 D — Agent 與模型</t>
+          <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>ADR-011</t>
+          <t>ADR-003</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>排程中</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Agent 整合風格三分類（MCP / HTTP-internal / 不暴露）</t>
+          <t>平台工程治理排程（migration 防漂移・API 收斂・CD）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>系統(agent)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>010 · 025 · 015</t>
+          <t>002 · 021 · 022</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
@@ -2744,12 +2776,12 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>群 D — Agent 與模型</t>
+          <t>群 B — 身分與授權</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ADR-012</t>
+          <t>ADR-004</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2759,7 +2791,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio 品牌自服務調校</t>
+          <t>Casdoor 統一 IdP + 租戶 + License 授權</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -2769,7 +2801,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>001 · 010 · 009 · 005 · 018</t>
+          <t>005 · 002 · 024</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
@@ -2777,22 +2809,22 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>群 E — 工單平台與流程自動化</t>
+          <t>群 B — 身分與授權</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>ADR-013</t>
+          <t>ADR-005</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Accepted（分期）</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Flow-as-Blocks 宣告式 DSL + 配置驅動引擎（DSL-first）</t>
+          <t>四方 RBAC 模型 + enforce（deny-by-default）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -2802,7 +2834,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>001 · 014 · 015</t>
+          <t>004 · 016 · 022</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
@@ -2810,22 +2842,22 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>群 E — 工單平台與流程自動化</t>
+          <t>群 C — 即時、事件與可觀測性</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>ADR-014</t>
+          <t>ADR-006</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>規劃中（北極星）</t>
+          <t>規劃中</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AI Onboarding Compiler + Block Ontology（護城河）</t>
+          <t>即時高併發骨幹（Kafka 事件 + Redis fanout + 讀寫分離）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -2835,7 +2867,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>013 · 018 · 001</t>
+          <t>002 · 016 · 017 · 007</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
@@ -2843,12 +2875,12 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>群 E — 工單平台與流程自動化</t>
+          <t>群 C — 即時、事件與可觀測性</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ADR-015</t>
+          <t>ADR-007</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2858,17 +2890,17 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>工單狀態機核心不變式（locksmith flow 首個實例）</t>
+          <t>可觀測性分層（SigNoz 系統監控 + OPIK Agent LLM Ops）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>系統(api)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>013 · 025 · 026</t>
+          <t>002 · 009 · 012</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
@@ -2876,12 +2908,12 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>群 F — 技師平台</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>ADR-016</t>
+          <t>ADR-008</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -2891,17 +2923,17 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>技師共享池獨立系統（跨租戶單一真相）</t>
+          <t>Agent 核心採 LockCore（fork nanobot 最小核心）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(agent)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>002 · 017 · 006 · 004</t>
+          <t>009 · 010 · 011 · 025</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
@@ -2909,12 +2941,12 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>群 F — 技師平台</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ADR-017</t>
+          <t>ADR-009</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2924,7 +2956,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>技師平台佣金邊界 + 工單可見性（CQRS 投影）</t>
+          <t>Model Orchestration Layer 供應商無關（LiteLLM 實作）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2934,7 +2966,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>016(refines) · 002 · 006</t>
+          <t>001 · 008 · 010 · 007</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
@@ -2942,12 +2974,12 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>群 G — 知識精煉與數據</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ADR-018</t>
+          <t>ADR-010</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -2957,17 +2989,17 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>知識精煉獨立服務（draft → HITL 審核 → 寫入）</t>
+          <t>知識分層：Skill 行為驅動 + RAG-via-MCP 檢索（從屬非收斂）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(agent)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>010 · 019 · 014 · 004</t>
+          <t>008 · 011 · 018 · 019 · 012</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
@@ -2975,12 +3007,12 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>群 G — 知識精煉與數據</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ADR-019</t>
+          <t>ADR-011</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2990,17 +3022,17 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Medallion 分層數據架構（raw→bronze→silver→refinery）</t>
+          <t>Agent 整合風格三分類（MCP / HTTP-internal / 不暴露）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>系統(data)</t>
+          <t>系統(agent)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>018 · 010</t>
+          <t>010 · 025 · 015</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
@@ -3008,12 +3040,12 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>群 G — 知識精煉與數據</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ADR-020</t>
+          <t>ADR-012</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3023,17 +3055,17 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>三庫物理隔離的租戶隔離模型</t>
+          <t>Agent Configuration Studio 品牌自服務調校</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>系統(data)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>002 · 016 · 017 · 021</t>
+          <t>001 · 010 · 009 · 005 · 018</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
@@ -3041,32 +3073,32 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>群 G — 知識精煉與數據</t>
+          <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ADR-021</t>
+          <t>ADR-013</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Accepted（分期）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>psycopg3 raw SQL + 純 SQL forward-only migration</t>
+          <t>Flow-as-Blocks 宣告式 DSL + 配置驅動引擎（DSL-first）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>系統(api/data)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>020 · 003</t>
+          <t>001 · 014 · 015</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -3074,32 +3106,32 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>群 H — API 與 Web 形態</t>
+          <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ADR-022</t>
+          <t>ADR-014</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>規劃中（北極星）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>API_SURFACE 單體多面塑形（一 codebase → 三暴露面）</t>
+          <t>AI Onboarding Compiler + Block Ontology（護城河）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>系統(api)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>005 · 004 · 006 · 002</t>
+          <t>013 · 018 · 001</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
@@ -3107,32 +3139,32 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>群 H — API 與 Web 形態</t>
+          <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ADR-023</t>
+          <t>ADR-015</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Superseded by 028</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>單一 codebase 以 APP_MODE build 多 portal</t>
+          <t>工單狀態機核心不變式（locksmith flow 首個實例）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>系統(web)</t>
+          <t>系統(api)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>022 · 024</t>
+          <t>013 · 025 · 026</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -3140,12 +3172,12 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>群 H — API 與 Web 形態</t>
+          <t>群 F — 技師平台</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>ADR-024</t>
+          <t>ADR-016</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3155,17 +3187,17 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>web 為 client SPA（無 BFF）+ Context 狀態 + OIDC 認證</t>
+          <t>技師共享池獨立系統（跨租戶單一真相）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>系統(web)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>023 · 004 · 005</t>
+          <t>002 · 017 · 006 · 004</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -3173,12 +3205,12 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>群 I — 領域安全紅線</t>
+          <t>群 F — 技師平台</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ADR-025</t>
+          <t>ADR-017</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -3188,7 +3220,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>AI 話術邊界與「永不自轉工單」紅線憲章</t>
+          <t>技師平台佣金邊界 + 工單可見性（CQRS 投影）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3198,7 +3230,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>011 · 015 · 012</t>
+          <t>016(refines) · 002 · 006</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr"/>
@@ -3206,12 +3238,12 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>群 I — 領域安全紅線</t>
+          <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ADR-026</t>
+          <t>ADR-018</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3221,17 +3253,17 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>報價快照 hash-chain 不可否認性</t>
+          <t>知識精煉獨立服務（draft → HITL 審核 → 寫入）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>系統(api)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>015 · 021</t>
+          <t>010 · 019 · 014 · 004</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
@@ -3239,12 +3271,12 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ADR-027</t>
+          <t>ADR-019</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3254,17 +3286,17 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>現場報價修正發起邊界——技師平台只發 command、品牌 api 為報價唯一權威</t>
+          <t>Medallion 分層數據架構（raw→bronze→silver→refinery）</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(data)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>016 · 017 · 026</t>
+          <t>018 · 010</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
@@ -3272,12 +3304,12 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>ADR-028</t>
+          <t>ADR-020</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3287,17 +3319,17 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>web 檔案層拆分——四站台完全獨立專案（複製分家）</t>
+          <t>三庫物理隔離的租戶隔離模型</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>系統(web)</t>
+          <t>系統(data)</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>supersedes 023 · 022 · 024</t>
+          <t>002 · 016 · 017 · 021</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -3305,12 +3337,12 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>ADR-029</t>
+          <t>ADR-021</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3320,17 +3352,17 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>知識產線雙軌重構——data/ 改名 knowledge-pipeline + facts/behavior 分軌 + provenance 治理</t>
+          <t>psycopg3 raw SQL + 純 SQL forward-only migration</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>系統(knowledge-pipeline)</t>
+          <t>系統(api/data)</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>010 · 018 · 019</t>
+          <t>020 · 003</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
@@ -3338,12 +3370,12 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>ADR-030</t>
+          <t>ADR-022</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3353,17 +3385,17 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>RAG-MCP＝對外開放介面；Skill 為知識與推理主軸（cutover 取消）</t>
+          <t>API_SURFACE 單體多面塑形（一 codebase → 三暴露面）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(api)</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>部分取代 010 · 011</t>
+          <t>005 · 004 · 006 · 002</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
@@ -3371,32 +3403,32 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>ADR-031</t>
+          <t>ADR-023</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Superseded by 028</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>契約工件三分層——前端型別 SoT＝runtime export；設計稿 spec 專職設計期契約</t>
+          <t>單一 codebase 以 APP_MODE build 多 portal</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>系統(api/web)</t>
+          <t>系統(web)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>refines 022 · 028</t>
+          <t>022 · 024</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
@@ -3404,12 +3436,12 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>ADR-032</t>
+          <t>ADR-024</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3419,17 +3451,17 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Skill 熱更新——品牌庫為 SSOT、image builtin 降級離線保底、workspace overlay 物化（≤60s 生效不重佈）</t>
+          <t>web 為 client SPA（無 BFF）+ Context 狀態 + OIDC 認證</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(web)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>延續 030 · 細化 CLAUDE.md Arch Lock 條 2</t>
+          <t>023 · 004 · 005</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -3437,41 +3469,503 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
+          <t>群 I — 領域安全紅線</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>ADR-025</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>AI 話術邊界與「永不自轉工單」紅線憲章</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>011 · 015 · 012</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>群 I — 領域安全紅線</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>ADR-026</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>報價快照 hash-chain 不可否認性</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>系統(api)</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>015 · 021</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>ADR-027</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>現場報價修正發起邊界——技師平台只發 command、品牌 api 為報價唯一權威</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>016 · 017 · 026</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>ADR-028</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>web 檔案層拆分——四站台完全獨立專案（複製分家）</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>系統(web)</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>supersedes 023 · 022 · 024</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>ADR-029</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>知識產線雙軌重構——data/ 改名 knowledge-pipeline + facts/behavior 分軌 + provenance 治理</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>系統(knowledge-pipeline)</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>010 · 018 · 019</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>ADR-030</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>RAG-MCP＝對外開放介面；Skill 為知識與推理主軸（cutover 取消）</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>部分取代 010 · 011</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>ADR-031</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>契約工件三分層——前端型別 SoT＝runtime export；設計稿 spec 專職設計期契約</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>系統(api/web)</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>refines 022 · 028</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>ADR-032</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Skill 熱更新——品牌庫為 SSOT、image builtin 降級離線保底、workspace overlay 物化（≤60s 生效不重佈）</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>延續 030 · 細化 CLAUDE.md Arch Lock 條 2</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>群 J — 跨系統流程邊界</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>ADR-033</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>轉真人判準——SOP 情境式紅線取代 FR-AGT-03 三輪硬計數（正典讓步；Clarify gate 降為話術原則；transfer 唯一出口不變）</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>系統(agent)</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
         <is>
           <t>025 · 008 · 032</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>ADR-034</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>規劃中</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>前端 Mutation 一致性、偏好分層與 Capability 導覽</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>系統(web/api)</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>refines 024 · 005 · 028</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>ADR-035</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>規劃中</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>租戶資源歸屬授權契約與 BOLA／IDOR 守門</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>平台/security</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>refines 005 · 020 · 022</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>ADR-036</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>規劃中（OD-001/004 gate）</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>機器身分與可撤銷服務憑證</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>平台/security</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>004 · 005 · 035</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>ADR-037</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>規劃中</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>背景工作 Runtime 從 API 生命週期拆分</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>系統(api/ops)</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>refines 006 · 003 · 021</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>ADR-038</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>規劃中</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>GCP 發版 Promotion 與證據關卡</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>平台/delivery</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>refines 003 · 002 · 007</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>ADR-039</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>規劃中（P2）</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>web 共享契約套件——四站獨立專案的窄例外</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>系統(web/tooling)</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>refines 028 · 031 · 034</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G76"/>
+  <autoFilter ref="A1:G90"/>
   <mergeCells count="2">
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A51:G51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -782,7 +782,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Decided</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Decided</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅ 2026-07-27（HTTP；跨 host realtime 另受網域 gate）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>ADR-034；2.1.1；OD-004 提供 principal/claim input</t>
+          <t>ADR-034；2.1.1；OD-004 已 closed（ADR-041：單一平台 principal + 品牌 membership）</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🟨 code ready／待 production gate</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ADR-036；OD-001／OD-004</t>
+          <t>ADR-036；ADR-040／ADR-041（OD-001／004 已 closed）</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🟨 pilot ready／待 GCP 演練</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>🟨 workflow ready／待外部環境</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>已實作</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>已實作</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>規劃中（OD-001/004 gate）</t>
+          <t>實作完成／待 production 取證（transport 已由 ADR-040 定版；餘 fallback 歸零）</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>Pilot code ready／待 GCP 取證</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>Workflow ready／待環境演練</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>規劃中（P2）</t>
+          <t>已實作（vendored 0.1.0）</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3961,8 +3961,74 @@
       </c>
       <c r="G90" s="5" t="inlineStr"/>
     </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>ADR-040</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Accepted（closes OD-001）</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>OHS 服務間憑證定版為受控 opaque credential</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>平台/security</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>036 · 004 · 035</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>ADR-041</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Accepted（closes OD-004）</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>跨品牌技師身分採單一平台 principal + 品牌 membership claim</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>平台/security</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>004 · 005 · 035</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G90"/>
+  <autoFilter ref="A1:G92"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A51:G51"/>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -832,7 +832,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Decided</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Decided</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⬜〔標注 2026-07-28：ADR-043 已定版師傅專屬 channel 由 technician-platform 持有，本列的「跨品牌聚合」自此有明確 owner；遷移仍待 Redis／Kafka 取證〕</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>FR-TEC-*；TC-DISPATCH-05 欄位最小化</t>
+          <t>FR-TEC-*；TC-DISPATCH-05 欄位最小化；ADR-043</t>
         </is>
       </c>
     </row>
@@ -2056,32 +2056,32 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=In Progress——0721 codegraph 稽核證 reconcile 閘門雛形 code 已在，生產未啟用〕</t>
+          <t>🛑 待裁決</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>期末對帳 reconcile 閘門（品牌計費 vs 平台結算對平）</t>
+          <t>混合派工：指派為主、搶單為輔（指定師傅逾時未接 → 釋出公開池）。現行為純指派制，offer／accept／搶單併發控制全部不存在</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BE+DT</t>
+          <t>PM+BE+FE+QA</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>CR-0191 §8 六項業主裁決；3.1.1；ADR-043</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>BR-SETTLE-05；FR-E03</t>
+          <t>CIA＝docs/4-exploration/CR-0191-hybrid-dispatch-assign-then-open-pool.md；併發承接「N 搶 1 恰好一成功」測試為硬門檻</t>
         </is>
       </c>
     </row>
@@ -2093,32 +2093,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=In Progress——0721 codegraph 稽核證 reconcile 閘門雛形 code 已在，生產未啟用〕</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>License → provisioning 自動化（開站流程腳本化）</t>
+          <t>期末對帳 reconcile 閘門（品牌計費 vs 平台結算對平）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>OPS</t>
+          <t>BE+DT</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>ADR-002（per-brand bundle）</t>
+          <t>BR-SETTLE-05；FR-E03</t>
         </is>
       </c>
     </row>
@@ -2130,32 +2130,32 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>3.4.1</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=Done——0719 tech/platform 面雲端部署＋技師庫上雲，B1 業主親證（0721 稽核輪改卡）；本列經業主確認後可打 ✅〕</t>
+          <t>⬜</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>雲端拓撲對齊（tech / platform 面雲端部署 + 技師庫上雲）</t>
+          <t>refinery intake 改走受控 API（ADR-042）：intake 端點 + DTO 資料最小化 + cursor/增量水位 + 逐租戶用量計量；REFINERY_POSTGRES_URI 直讀加 usage counter 後退場</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>OPS</t>
+          <t>BE+DT</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>ADR-042；ADR-036/040 憑證</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>平台 L1 G-01 收斂</t>
+          <t>收費服務前置：逐租戶計量可出帳；直讀使用量連續一個 release window = 0</t>
         </is>
       </c>
     </row>
@@ -2167,106 +2167,106 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>3.5.1</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>⬜</t>
+          <t>⬜〔標注 2026-07-28：ADR-042 生效後，開站不再需要為 refinery 額外配 DB 憑證與網路路徑——本列的 provisioning 腳本應以 service principal 取代之〕</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>第 2 品牌租戶開站演練（全流程 dry-run：申請 → 核准 → 開站 → 綁 LINE）</t>
+          <t>License → provisioning 自動化（開站流程腳本化）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>PM+OPS</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>開站 SOP 文件化；M3 Release gate</t>
+          <t>ADR-002（per-brand bundle）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
+          <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>3.6.1</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=Done——0719 tech/platform 面雲端部署＋技師庫上雲，B1 業主親證（0721 稽核輪改卡）；本列經業主確認後可打 ✅〕</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-07-27</t>
+          <t>雲端拓撲對齊（tech / platform 面雲端部署 + 技師庫上雲）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>前端 mutation contract：optimistic／server-confirmed 分級、rollback、精準 invalidation、action idempotency、409 conflict UX</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>FE+BE+QA</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>ADR-034</t>
+          <t>平台 L1 G-01 收斂</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
+          <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>3.6.2</t>
+          <t>3.5.1</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>⬜</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-07-27（HTTP；跨 host realtime 另受網域 gate）</t>
+          <t>第 2 品牌租戶開站演練（全流程 dry-run：申請 → 核准 → 開站 → 綁 LINE）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>偏好與登入資料分層：三庫 user_preferences allowlist、跨裝置同步；localStorage token 退場</t>
+          <t>PM+OPS</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>FE+BE+DT</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>ADR-034；2.1.1；OD-004 已 closed（ADR-041：單一平台 principal + 品牌 membership）</t>
+          <t>開站 SOP 文件化；M3 Release gate</t>
         </is>
       </c>
     </row>
@@ -2278,32 +2278,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>3.6.3</t>
+          <t>3.6.1</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-07-27</t>
+          <t>前端 mutation contract：optimistic／server-confirmed 分級、rollback、精準 invalidation、action idempotency、409 conflict UX</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Brand Portal Capability-driven Command Palette v1</t>
+          <t>FE+BE+QA</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>FE+BE</t>
+          <t>ADR-034</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>3.6.2；ADR-034</t>
+          <t>shared-contract/mutation + Notification reference；offline/retry、5xx、409 Playwright 3/3，同 action key 重送與 rollback 已證</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.6.2</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>✅ 2026-07-27（HTTP；跨 host realtime 另受網域 gate）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-07-27</t>
+          <t>偏好與登入資料分層：三庫 user_preferences allowlist、跨裝置同步；localStorage token 退場</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>API resource ownership matrix 與 BOLA／IDOR parameterized contract tests</t>
+          <t>FE+BE+DT</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>SEC+BE+QA</t>
+          <t>ADR-034；2.1.1；OD-004 已 closed（ADR-041：單一平台 principal + 品牌 membership）</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>ADR-035</t>
+          <t>migration 120 二套；三面 API/CAS/16 KiB tests；四站 same-origin proxy + HttpOnly cookie；browser token scanner 通過</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>🟨 code ready／待 production gate</t>
+          <t>Brand Portal Capability-driven Command Palette v1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Service principal／credential lifecycle：hash、scope、expiry、rotation、revoke、audit；遷移共用 X-Internal-Token</t>
+          <t>FE+BE</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Platform+SEC+BE</t>
+          <t>3.6.2；ADR-034</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ADR-036；ADR-040／ADR-041（OD-001／004 已 closed）</t>
+          <t>Ctrl/⌘+K；搜尋／草稿／佇列／通知／saved view；capability + rolePolicy 雙過濾，unit/build 通過</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2389,32 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>3.6.6</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>✅ 2026-07-27</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>🟨 pilot ready／待 GCP 演練</t>
+          <t>API resource ownership matrix 與 BOLA／IDOR parameterized contract tests</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Background runtime 拆分：job registry、worker entrypoint、Cloud Scheduler/Run Job pilot、outbox metrics</t>
+          <t>SEC+BE+QA</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>BE+OPS</t>
+          <t>ADR-035</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>ADR-037；GCP IAM/Scheduler</t>
+          <t>runtime mutation + sensitive read/export 100% 分類；六類 contract 皆綁 real negative test node id，CI completeness 通過</t>
         </is>
       </c>
     </row>
@@ -2426,32 +2426,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>3.6.7</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>🟨 code ready／待 production gate</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>🟨 workflow ready／待外部環境</t>
+          <t>Service principal／credential lifecycle：hash、scope、expiry、rotation、revoke、audit；遷移共用 X-Internal-Token</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>GCP staging→production promotion、GitHub Environments、WIF 隔離、release manifest、rollback/restore evidence</t>
+          <t>Platform+SEC+BE</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>OPS+QA+SEC</t>
+          <t>ADR-036；ADR-040／ADR-041（OD-001／004 已 closed）</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>ADR-038；3.6.4；3.6.6</t>
+          <t>migration 121、API/auth/caller/負測已綠；transport/claim 已定案（ADR-040／041）；尚缺 principal/secret bootstrap 與 fallback usage 連續一個 release window = 0</t>
         </is>
       </c>
     </row>
@@ -2463,82 +2463,106 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>3.6.8</t>
+          <t>3.6.6</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>🟨 pilot ready／待 GCP 演練</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>✅ 2026-07-27</t>
+          <t>Background runtime 拆分：job registry、worker entrypoint、Cloud Scheduler/Run Job pilot、outbox metrics</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>web/shared-contract 版本化窄例外：runtime types、RFC7807、mutation/conflict、capability contract</t>
+          <t>BE+OPS</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>FE+OPS</t>
+          <t>ADR-037；GCP IAM/Scheduler</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>ADR-039；3.6.1；ADR-031 runtime export</t>
+          <t>14-job registry、獨立 entrypoint、hybrid cutover flag、六項 SLI、Cloud Run Job 腳本已綠；尚缺真實 shadow→cutover→rollback／重跑證據</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
+          <t>3.6.7</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>🟨 workflow ready／待外部環境</t>
+        </is>
+      </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>flow DSL 引擎產品化</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="5" t="inlineStr"/>
+          <t>GCP staging→production promotion、GitHub Environments、WIF 隔離、release manifest、rollback/restore evidence</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>OPS+QA+SEC</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>ADR-038；3.6.4；3.6.6</t>
+        </is>
+      </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>從鎖匠 pack 抽出引擎（DSL-first 鐵律：引擎先於 UI）；積木契約 + 匯入靜態驗證 / ADR-013；15_SDS §3.3-3.5</t>
+          <t>同 digest workflow、雙環境 manifest、health/smoke、rollback/drill tooling 已綠；2026-07-27 稽核 repo Environments=0、Actions vars/secrets=0，且私有 repo 目前方案拒絕 branch protection／required reviewer（403）；尚缺 WIF 與 rollback/forward-fix/restore 真實演練</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>M4 / M5 平台化（概要層級）</t>
+          <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr"/>
+          <t>3.6.8</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>✅ 2026-07-27</t>
+        </is>
+      </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>兩層渲染</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr"/>
+          <t>web/shared-contract 版本化窄例外：runtime types、RFC7807、mutation/conflict、capability contract</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>FE+OPS</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>ADR-039；3.6.1；ADR-031 runtime export</t>
+        </is>
+      </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>field_metadata 配置驅動（DynamicForm/Table）+ ui_composition 元件組裝；現行鎖匠前端漸進遷移，不 big-bang 重寫 / ADR-001；07_workorder §8.1</t>
+          <t>0.1.0 immutable vendored tarball；boundary/test/build、consumer matrix、四站 lockfile/tsc/production build 全綠；Next/PostCSS/sharp/brace-expansion 修補後完整 audit 皆 0 vulnerability</t>
         </is>
       </c>
     </row>
@@ -2550,20 +2574,20 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Vertical Pack 打包</t>
+          <t>flow DSL 引擎產品化</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>pack@version + 租戶覆寫 + 向後相容檢查；鎖匠版收斂為第一個正式 pack / 07_workorder §4</t>
+          <t>從鎖匠 pack 抽出引擎（DSL-first 鐵律：引擎先於 UI）；積木契約 + 匯入靜態驗證 / ADR-013；15_SDS §3.3-3.5</t>
         </is>
       </c>
     </row>
@@ -2575,20 +2599,20 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>積木庫 bootstrap</t>
+          <t>兩層渲染</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>頭 2-3 產業積木手工建（誠實面對冷啟動） / ADR-014 鐵律 2</t>
+          <t>field_metadata 配置驅動（DynamicForm/Table）+ ui_composition 元件組裝；現行鎖匠前端漸進遷移，不 big-bang 重寫 / ADR-001；07_workorder §8.1</t>
         </is>
       </c>
     </row>
@@ -2600,20 +2624,20 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>FlowEditor 拖拉</t>
+          <t>Vertical Pack 打包</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>薄編輯器，只產出/編修 DSL / FR-F07</t>
+          <t>pack@version + 租戶覆寫 + 向後相容檢查；鎖匠版收斂為第一個正式 pack / 07_workorder §4</t>
         </is>
       </c>
     </row>
@@ -2625,20 +2649,20 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>AI Onboarding Compiler</t>
+          <t>積木庫 bootstrap</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>SOP/訪談 → Block Ontology → draft DSL → HITL 人審（金流/派工/同意書必過人審）；與 knowledge-refinery 共用審核 UI 骨架 / ADR-014 / FR-F08</t>
+          <t>頭 2-3 產業積木手工建（誠實面對冷啟動） / ADR-014 鐵律 2</t>
         </is>
       </c>
     </row>
@@ -2650,95 +2674,79 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>第 2 產業落地</t>
+          <t>FlowEditor 拖拉</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>薄編輯器，只產出/編修 DSL / FR-F07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>AI Onboarding Compiler</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>SOP/訪談 → Block Ontology → draft DSL → HITL 人審（金流/派工/同意書必過人審）；與 knowledge-refinery 共用審核 UI 骨架 / ADR-014 / FR-F08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>M4 / M5 平台化（概要層級）</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>第 2 產業落地</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
           <t>FDE 4 配置面走通（診斷 / 知識精煉 / flow / UI 組裝），驗證飛輪 / 07_workorder §8.2</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>ADR —— 14_ADR/00_INDEX.md（append-only，不改舊內容）</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>群 A — 平台奠基與部署</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>ADR-001</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>平台核心 vs 領域配置分層（TRIZ 按系統層級分離）</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>009 · 013 · 014 · 002</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>群 A — 平台奠基與部署</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>ADR-002</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>per-brand 授權部署（大單體 + 內部容器 + 集中共用元件）</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>004 · 016 · 020 · 006</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -2748,17 +2756,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>ADR-003</t>
+          <t>ADR-001</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>排程中</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>平台工程治理排程（migration 防漂移・API 收斂・CD）</t>
+          <t>平台核心 vs 領域配置分層（TRIZ 按系統層級分離）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -2768,7 +2776,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>002 · 021 · 022</t>
+          <t>009 · 013 · 014 · 002</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
@@ -2776,12 +2784,12 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>群 B — 身分與授權</t>
+          <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>ADR-004</t>
+          <t>ADR-002</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2791,7 +2799,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Casdoor 統一 IdP + 租戶 + License 授權</t>
+          <t>per-brand 授權部署（大單體 + 內部容器 + 集中共用元件）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -2801,7 +2809,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>005 · 002 · 024</t>
+          <t>004 · 016 · 020 · 006</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
@@ -2809,22 +2817,22 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>群 B — 身分與授權</t>
+          <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>ADR-005</t>
+          <t>ADR-003</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>排程中</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>四方 RBAC 模型 + enforce（deny-by-default）</t>
+          <t>平台工程治理排程（migration 防漂移・API 收斂・CD）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -2834,7 +2842,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>004 · 016 · 022</t>
+          <t>002 · 021 · 022</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
@@ -2842,22 +2850,22 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>群 C — 即時、事件與可觀測性</t>
+          <t>群 B — 身分與授權</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>ADR-006</t>
+          <t>ADR-004</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>規劃中</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>即時高併發骨幹（Kafka 事件 + Redis fanout + 讀寫分離）</t>
+          <t>Casdoor 統一 IdP + 租戶 + License 授權</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -2867,7 +2875,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>002 · 016 · 017 · 007</t>
+          <t>005 · 002 · 024</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
@@ -2875,12 +2883,12 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>群 C — 即時、事件與可觀測性</t>
+          <t>群 B — 身分與授權</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ADR-007</t>
+          <t>ADR-005</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2890,7 +2898,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>可觀測性分層（SigNoz 系統監控 + OPIK Agent LLM Ops）</t>
+          <t>四方 RBAC 模型 + enforce（deny-by-default）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -2900,7 +2908,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>002 · 009 · 012</t>
+          <t>004 · 016 · 022</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
@@ -2908,32 +2916,32 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>群 D — Agent 與模型</t>
+          <t>群 C — 即時、事件與可觀測性</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>ADR-008</t>
+          <t>ADR-006</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>規劃中</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Agent 核心採 LockCore（fork nanobot 最小核心）</t>
+          <t>即時高併發骨幹（Kafka 事件 + Redis fanout + 讀寫分離）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>系統(agent)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>009 · 010 · 011 · 025</t>
+          <t>002 · 016 · 017 · 007</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
@@ -2941,12 +2949,12 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>群 D — Agent 與模型</t>
+          <t>群 C — 即時、事件與可觀測性</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>ADR-009</t>
+          <t>ADR-007</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2956,7 +2964,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Model Orchestration Layer 供應商無關（LiteLLM 實作）</t>
+          <t>可觀測性分層（SigNoz 系統監控 + OPIK Agent LLM Ops）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2966,7 +2974,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>001 · 008 · 010 · 007</t>
+          <t>002 · 009 · 012</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr"/>
@@ -2979,7 +2987,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ADR-010</t>
+          <t>ADR-008</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -2989,7 +2997,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>知識分層：Skill 行為驅動 + RAG-via-MCP 檢索（從屬非收斂）</t>
+          <t>Agent 核心採 LockCore（fork nanobot 最小核心）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2999,7 +3007,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>008 · 011 · 018 · 019 · 012</t>
+          <t>009 · 010 · 011 · 025</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr"/>
@@ -3012,7 +3020,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ADR-011</t>
+          <t>ADR-009</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3022,17 +3030,17 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Agent 整合風格三分類（MCP / HTTP-internal / 不暴露）</t>
+          <t>Model Orchestration Layer 供應商無關（LiteLLM 實作）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>系統(agent)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>010 · 025 · 015</t>
+          <t>001 · 008 · 010 · 007</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
@@ -3045,7 +3053,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ADR-012</t>
+          <t>ADR-010</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3055,17 +3063,17 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio 品牌自服務調校</t>
+          <t>知識分層：Skill 行為驅動 + RAG-via-MCP 檢索（從屬非收斂）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(agent)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>001 · 010 · 009 · 005 · 018</t>
+          <t>008 · 011 · 018 · 019 · 012</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
@@ -3073,32 +3081,32 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>群 E — 工單平台與流程自動化</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ADR-013</t>
+          <t>ADR-011</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Accepted（分期）</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Flow-as-Blocks 宣告式 DSL + 配置驅動引擎（DSL-first）</t>
+          <t>Agent 整合風格三分類（MCP / HTTP-internal / 不暴露）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(agent)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>001 · 014 · 015</t>
+          <t>010 · 025 · 015</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -3106,22 +3114,22 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>群 E — 工單平台與流程自動化</t>
+          <t>群 D — Agent 與模型</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ADR-014</t>
+          <t>ADR-012</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>規劃中（北極星）</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>AI Onboarding Compiler + Block Ontology（護城河）</t>
+          <t>Agent Configuration Studio 品牌自服務調校</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -3131,7 +3139,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>013 · 018 · 001</t>
+          <t>001 · 010 · 009 · 005 · 018</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
@@ -3144,27 +3152,27 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>ADR-015</t>
+          <t>ADR-013</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Accepted（分期）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>工單狀態機核心不變式（locksmith flow 首個實例）</t>
+          <t>Flow-as-Blocks 宣告式 DSL + 配置驅動引擎（DSL-first）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>系統(api)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>013 · 025 · 026</t>
+          <t>001 · 014 · 015</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -3172,22 +3180,22 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>群 F — 技師平台</t>
+          <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>ADR-016</t>
+          <t>ADR-014</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>規劃中（北極星）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>技師共享池獨立系統（跨租戶單一真相）</t>
+          <t>AI Onboarding Compiler + Block Ontology（護城河）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3197,7 +3205,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>002 · 017 · 006 · 004</t>
+          <t>013 · 018 · 001</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -3205,12 +3213,12 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>群 F — 技師平台</t>
+          <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>ADR-017</t>
+          <t>ADR-015</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -3220,17 +3228,17 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>技師平台佣金邊界 + 工單可見性（CQRS 投影）</t>
+          <t>工單狀態機核心不變式（locksmith flow 首個實例）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(api)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>016(refines) · 002 · 006</t>
+          <t>013 · 025 · 026</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr"/>
@@ -3238,12 +3246,12 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>群 G — 知識精煉與數據</t>
+          <t>群 F — 技師平台</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>ADR-018</t>
+          <t>ADR-016</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3253,7 +3261,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>知識精煉獨立服務（draft → HITL 審核 → 寫入）</t>
+          <t>技師共享池獨立系統（跨租戶單一真相）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -3263,7 +3271,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>010 · 019 · 014 · 004</t>
+          <t>002 · 017 · 006 · 004</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
@@ -3271,12 +3279,12 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>群 G — 知識精煉與數據</t>
+          <t>群 F — 技師平台</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ADR-019</t>
+          <t>ADR-017</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3286,17 +3294,17 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Medallion 分層數據架構（raw→bronze→silver→refinery）</t>
+          <t>技師平台佣金邊界 + 工單可見性（CQRS 投影）</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>系統(data)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>018 · 010</t>
+          <t>016(refines) · 002 · 006</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
@@ -3309,7 +3317,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>ADR-020</t>
+          <t>ADR-018</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3319,17 +3327,17 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>三庫物理隔離的租戶隔離模型</t>
+          <t>知識精煉獨立服務（draft → HITL 審核 → 寫入）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>系統(data)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>002 · 016 · 017 · 021</t>
+          <t>010 · 019 · 014 · 004</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr"/>
@@ -3342,7 +3350,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>ADR-021</t>
+          <t>ADR-019</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -3352,17 +3360,17 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>psycopg3 raw SQL + 純 SQL forward-only migration</t>
+          <t>Medallion 分層數據架構（raw→bronze→silver→refinery）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>系統(api/data)</t>
+          <t>系統(data)</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>020 · 003</t>
+          <t>018 · 010</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr"/>
@@ -3370,12 +3378,12 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>群 H — API 與 Web 形態</t>
+          <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>ADR-022</t>
+          <t>ADR-020</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3385,17 +3393,17 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>API_SURFACE 單體多面塑形（一 codebase → 三暴露面）</t>
+          <t>三庫物理隔離的租戶隔離模型</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>系統(api)</t>
+          <t>系統(data)</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>005 · 004 · 006 · 002</t>
+          <t>002 · 016 · 017 · 021</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
@@ -3403,32 +3411,32 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>群 H — API 與 Web 形態</t>
+          <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>ADR-023</t>
+          <t>ADR-021</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Superseded by 028</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>單一 codebase 以 APP_MODE build 多 portal</t>
+          <t>psycopg3 raw SQL + 純 SQL forward-only migration</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>系統(web)</t>
+          <t>系統(api/data)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>022 · 024</t>
+          <t>020 · 003</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
@@ -3441,7 +3449,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>ADR-024</t>
+          <t>ADR-022</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3451,17 +3459,17 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>web 為 client SPA（無 BFF）+ Context 狀態 + OIDC 認證</t>
+          <t>API_SURFACE 單體多面塑形（一 codebase → 三暴露面）</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>系統(web)</t>
+          <t>系統(api)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>023 · 004 · 005</t>
+          <t>005 · 004 · 006 · 002</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -3469,32 +3477,32 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>群 I — 領域安全紅線</t>
+          <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>ADR-025</t>
+          <t>ADR-023</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Superseded by 028</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>AI 話術邊界與「永不自轉工單」紅線憲章</t>
+          <t>單一 codebase 以 APP_MODE build 多 portal</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(web)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>011 · 015 · 012</t>
+          <t>022 · 024</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr"/>
@@ -3502,12 +3510,12 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>群 I — 領域安全紅線</t>
+          <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>ADR-026</t>
+          <t>ADR-024</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3517,17 +3525,17 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>報價快照 hash-chain 不可否認性</t>
+          <t>web 為 client SPA（無 BFF）+ Context 狀態 + OIDC 認證</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>系統(api)</t>
+          <t>系統(web)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>015 · 021</t>
+          <t>023 · 004 · 005</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr"/>
@@ -3535,12 +3543,12 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 I — 領域安全紅線</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>ADR-027</t>
+          <t>ADR-025</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3550,7 +3558,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>現場報價修正發起邊界——技師平台只發 command、品牌 api 為報價唯一權威</t>
+          <t>AI 話術邊界與「永不自轉工單」紅線憲章</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -3560,7 +3568,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>016 · 017 · 026</t>
+          <t>011 · 015 · 012</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -3568,12 +3576,12 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>群 J — 跨系統流程邊界</t>
+          <t>群 I — 領域安全紅線</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>ADR-028</t>
+          <t>ADR-026</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -3583,17 +3591,17 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>web 檔案層拆分——四站台完全獨立專案（複製分家）</t>
+          <t>報價快照 hash-chain 不可否認性</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>系統(web)</t>
+          <t>系統(api)</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>supersedes 023 · 022 · 024</t>
+          <t>015 · 021</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr"/>
@@ -3606,7 +3614,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>ADR-029</t>
+          <t>ADR-027</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3616,17 +3624,17 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>知識產線雙軌重構——data/ 改名 knowledge-pipeline + facts/behavior 分軌 + provenance 治理</t>
+          <t>現場報價修正發起邊界——技師平台只發 command、品牌 api 為報價唯一權威</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>系統(knowledge-pipeline)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>010 · 018 · 019</t>
+          <t>016 · 017 · 026</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
@@ -3639,7 +3647,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>ADR-030</t>
+          <t>ADR-028</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -3649,17 +3657,17 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>RAG-MCP＝對外開放介面；Skill 為知識與推理主軸（cutover 取消）</t>
+          <t>web 檔案層拆分——四站台完全獨立專案（複製分家）</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>系統(web)</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>部分取代 010 · 011</t>
+          <t>supersedes 023 · 022 · 024</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr"/>
@@ -3672,7 +3680,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>ADR-031</t>
+          <t>ADR-029</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -3682,17 +3690,17 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>契約工件三分層——前端型別 SoT＝runtime export；設計稿 spec 專職設計期契約</t>
+          <t>知識產線雙軌重構——data/ 改名 knowledge-pipeline + facts/behavior 分軌 + provenance 治理</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>系統(api/web)</t>
+          <t>系統(knowledge-pipeline)</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>refines 022 · 028</t>
+          <t>010 · 018 · 019</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr"/>
@@ -3705,7 +3713,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>ADR-032</t>
+          <t>ADR-030</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -3715,7 +3723,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Skill 熱更新——品牌庫為 SSOT、image builtin 降級離線保底、workspace overlay 物化（≤60s 生效不重佈）</t>
+          <t>RAG-MCP＝對外開放介面；Skill 為知識與推理主軸（cutover 取消）</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -3725,7 +3733,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>延續 030 · 細化 CLAUDE.md Arch Lock 條 2</t>
+          <t>部分取代 010 · 011</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr"/>
@@ -3738,7 +3746,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ADR-033</t>
+          <t>ADR-031</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3748,17 +3756,17 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>轉真人判準——SOP 情境式紅線取代 FR-AGT-03 三輪硬計數（正典讓步；Clarify gate 降為話術原則；transfer 唯一出口不變）</t>
+          <t>契約工件三分層——前端型別 SoT＝runtime export；設計稿 spec 專職設計期契約</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>系統(agent)</t>
+          <t>系統(api/web)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>025 · 008 · 032</t>
+          <t>refines 022 · 028</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr"/>
@@ -3766,32 +3774,32 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>群 K — 體驗、安全執行與交付治理</t>
+          <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>ADR-034</t>
+          <t>ADR-032</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>已實作</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>前端 Mutation 一致性、偏好分層與 Capability 導覽</t>
+          <t>Skill 熱更新——品牌庫為 SSOT、image builtin 降級離線保底、workspace overlay 物化（≤60s 生效不重佈）</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>系統(web/api)</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>refines 024 · 005 · 028</t>
+          <t>延續 030 · 細化 CLAUDE.md Arch Lock 條 2</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -3799,32 +3807,32 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>群 K — 體驗、安全執行與交付治理</t>
+          <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>ADR-035</t>
+          <t>ADR-033</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>已實作</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>租戶資源歸屬授權契約與 BOLA／IDOR 守門</t>
+          <t>轉真人判準——SOP 情境式紅線取代 FR-AGT-03 三輪硬計數（正典讓步；Clarify gate 降為話術原則；transfer 唯一出口不變）</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>平台/security</t>
+          <t>系統(agent)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>refines 005 · 020 · 022</t>
+          <t>025 · 008 · 032</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr"/>
@@ -3837,27 +3845,27 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>ADR-036</t>
+          <t>ADR-034</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>實作完成／待 production 取證（transport 已由 ADR-040 定版；餘 fallback 歸零）</t>
+          <t>已實作</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>機器身分與可撤銷服務憑證</t>
+          <t>前端 Mutation 一致性、偏好分層與 Capability 導覽</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>平台/security</t>
+          <t>系統(web/api)</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>004 · 005 · 035</t>
+          <t>refines 024 · 005 · 028</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr"/>
@@ -3870,27 +3878,27 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ADR-037</t>
+          <t>ADR-035</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Pilot code ready／待 GCP 取證</t>
+          <t>已實作</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>背景工作 Runtime 從 API 生命週期拆分</t>
+          <t>租戶資源歸屬授權契約與 BOLA／IDOR 守門</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>系統(api/ops)</t>
+          <t>平台/security</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>refines 006 · 003 · 021</t>
+          <t>refines 005 · 020 · 022</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr"/>
@@ -3903,27 +3911,27 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>ADR-038</t>
+          <t>ADR-036</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Workflow ready／待環境演練</t>
+          <t>實作完成／待 production 取證（transport 已由 ADR-040 定版；餘 fallback 歸零）</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>GCP 發版 Promotion 與證據關卡</t>
+          <t>機器身分與可撤銷服務憑證</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>平台/delivery</t>
+          <t>平台/security</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>refines 003 · 002 · 007</t>
+          <t>004 · 005 · 035</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -3936,27 +3944,27 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>ADR-039</t>
+          <t>ADR-037</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>已實作（vendored 0.1.0）</t>
+          <t>Pilot code ready／待 GCP 取證</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>web 共享契約套件——四站獨立專案的窄例外</t>
+          <t>背景工作 Runtime 從 API 生命週期拆分</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>系統(web/tooling)</t>
+          <t>系統(api/ops)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>refines 028 · 031 · 034</t>
+          <t>refines 006 · 003 · 021</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr"/>
@@ -3969,27 +3977,27 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>ADR-040</t>
+          <t>ADR-038</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Accepted（closes OD-001）</t>
+          <t>Workflow ready／待環境演練</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>OHS 服務間憑證定版為受控 opaque credential</t>
+          <t>GCP 發版 Promotion 與證據關卡</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>平台/security</t>
+          <t>平台/delivery</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>036 · 004 · 035</t>
+          <t>refines 003 · 002 · 007</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr"/>
@@ -4002,36 +4010,168 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
+          <t>ADR-039</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>已實作（vendored 0.1.0）</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>web 共享契約套件——四站獨立專案的窄例外</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>系統(web/tooling)</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>refines 028 · 031 · 034</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>ADR-040</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Accepted（closes OD-001）</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>OHS 服務間憑證定版為受控 opaque credential</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>平台/security</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>036 · 004 · 035</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
           <t>ADR-041</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Accepted（closes OD-004）</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>跨品牌技師身分採單一平台 principal + 品牌 membership claim</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>平台/security</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr">
         <is>
           <t>004 · 005 · 035</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>ADR-042</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Accepted（closes OD-002）／intake 端點待實作</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>knowledge-refinery 資料進入契約定版為受控 API</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>平台/data</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>018 · 036 · 040</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>ADR-043</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Accepted（closes OD-003）／待 Redis/Kafka 取證</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>技師即時 channel 歸屬 technician-platform</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>平台/realtime</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>041 · 006 · 017</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G92"/>
+  <autoFilter ref="A1:G96"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A53:G53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -581,65 +581,141 @@
       <c r="A7" s="1" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>黃色欄位</t>
+          <t>Plane 詞彙對照</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
+          <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>灰色欄位</t>
+          <t xml:space="preserve">  里程碑 M1–M5</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+          <t>Plane 的 Milestone（Issue.milestone，單值，所以一張卡只能掛一個節點）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>白色欄位</t>
+          <t xml:space="preserve">  階段一 / 階段二</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>正典敘述，同樣改上游。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="1" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>Plane 的 Initiative（workspace 級，掛專案而非掛卡）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WBS 工作包</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Task（level 3）。它有負責人與前置依賴、用技術語彙，是交付物分解不是價值切片——不要為了湊 Story 層把它改寫成「作為…我想要…」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>四個狀態軸不得互推</t>
+          <t xml:space="preserve">  本表的缺口 ≠ 出貨閘門的 blocker</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+          <t>本表 ② 是「規格側」的追溯缺口（V2/V7/V8/V9/V10，設計有沒有接好）；Plane 出貨閘門的 blocker 是「執行側」的五類（failed／blocked／未結缺陷／未執行／已排程卻零契約）。兩套各自成立、不得互推——設計全綠不代表跑得過，反之亦然。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  本專案目前沒有 Cycle</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Cycle 是迭代時間盒。本專案的排程只到 Milestone 層，尚未建任何 cycle；在那之前「這個 sprint 交付什麼」這個問題沒有載體。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>黃色欄位</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>只有人能填。系統不會、也不該幫你填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>灰色欄位</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>白色欄位</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>正典敘述，同樣改上游。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>四個狀態軸不得互推</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
@@ -971,7 +1047,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>里程碑 / 群</t>
+          <t>里程碑（Milestone）/ 群</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
@@ -1008,7 +1084,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>WBS —— 27_Product_Roadmap_WBS.md</t>
+          <t>WBS 工作包（Plane 的 Task 層）—— 27_Product_Roadmap_WBS.md</t>
         </is>
       </c>
     </row>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 缺口與決策清單" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 里程碑與已定案決策" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 迭代計畫（每週衝刺）" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 迭代計畫（每週衝刺）'!$A$1:$K$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -131,6 +133,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -498,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -577,145 +582,169 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>③ 與 ④ 差在哪</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>③ 回答「有哪些工作」，④ 回答「哪一週做」。排程算不出來——前置依賴只給得出「不能早於」，給不出「應該在哪一週」，所以 ④ 的來源是宣告檔 _relations/sprint_plan.yaml，一列一個決定。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>④ 底下那兩段紅字要看</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>「待裁決」是卡在人身上、不是卡在工程；「明確排除」是範圍砍掉的決定。兩者都刻意指名——不指名的話，期末沒做完會被讀成滑期，而它從一開始就不在範圍內。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="1" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>Plane 詞彙對照</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  里程碑 M1–M5</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Plane 的 Milestone（Issue.milestone，單值，所以一張卡只能掛一個節點）。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  階段一 / 階段二</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Plane 的 Initiative（workspace 級，掛專案而非掛卡）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WBS 工作包</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Plane 的 Task（level 3）。它有負責人與前置依賴、用技術語彙，是交付物分解不是價值切片——不要為了湊 Story 層把它改寫成「作為…我想要…」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  本表的缺口 ≠ 出貨閘門的 blocker</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>本表 ② 是「規格側」的追溯缺口（V2/V7/V8/V9/V10，設計有沒有接好）；Plane 出貨閘門的 blocker 是「執行側」的五類（failed／blocked／未結缺陷／未執行／已排程卻零契約）。兩套各自成立、不得互推——設計全綠不代表跑得過，反之亦然。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  WBS 工作包</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Task（level 3）。它有負責人與前置依賴、用技術語彙，是交付物分解不是價值切片——不要為了湊 Story 層把它改寫成「作為…我想要…」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本表的缺口 ≠ 出貨閘門的 blocker</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>本表 ② 是「規格側」的追溯缺口（V2/V7/V8/V9/V10，設計有沒有接好）；Plane 出貨閘門的 blocker 是「執行側」的五類（failed／blocked／未結缺陷／未執行／已排程卻零契約）。兩套各自成立、不得互推——設計全綠不代表跑得過，反之亦然。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">  本專案目前沒有 Cycle</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Plane 的 Cycle 是迭代時間盒。本專案的排程只到 Milestone 層，尚未建任何 cycle；在那之前「這個 sprint 交付什麼」這個問題沒有載體。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="1" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>黃色欄位</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>灰色欄位</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
-        </is>
-      </c>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>黃色欄位</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>只有人能填。系統不會、也不該幫你填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>灰色欄位</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>白色欄位</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>正典敘述，同樣改上游。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>四個狀態軸不得互推</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
@@ -4251,4 +4280,1187 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>衝刺</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>衝刺目標</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>WBS</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>工作包</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>目前狀態</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>前置</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>本衝刺完成？</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>實際完成日</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27 ~ 2026-08-02</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>可觀測性與 CD 兩條 M1 尾巴收乾淨，讓 M2 的前置條件成立</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>1.4.1</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>可觀測性：SigNoz（metrics/logs/traces/alerts）+ OPIK（LLM 品質）基線</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>🔶 code 面 ✅（CR-0136 api＋CR-0156 agent/ref</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27 ~ 2026-08-02</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>可觀測性與 CD 兩條 M1 尾巴收乾淨，讓 M2 的前置條件成立</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>1.6.1</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>基礎 CD：3 Cloud Run 自動部署 + migration drift-check CI</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>🔶 drift-check ✅ 2026-07-09（CR-0136：migra</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-09</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Casdoor 統一 IdP、技師平台獨立、v1 API 收斂三線並行</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Casdoor 統一 IdP：org（租戶）/ OIDC 授權碼流 / License 訂閱管理</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>🔶 R1 ✅ 2026-07-10（CR-0141：Casdoor 部署 pro</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-09</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Casdoor 統一 IdP、技師平台獨立、v1 API 收斂三線並行</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2.4.1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>technician-platform 獨立系統：技師庫 + tech-api + 師傅 web 拆出</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>🔶 方案A/B 已落地（CR-0112：雙 stack＋技師身分權威庫拆分＋投影</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03 ~ 2026-08-09</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Casdoor 統一 IdP、技師平台獨立、v1 API 收斂三線並行</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2.5.1</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>v1 API 收斂：凍結 → 遷移 ~42 caller → 移除（5-gate）</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>🔶 Gate-1 凍結 enforced 2026-07-10（CR-0145：</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-16</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>M2 SIT+UAT 通過；憑證生命週期與背景 runtime 拆分落地</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2.6.1</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>M2 SIT + UAT（含跨系統整合場景）</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>🔶 SIT ✅ 2026-07-10（CR-0147：api 1738＋agen</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>2.1–2.5</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-16</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>M2 SIT+UAT 通過；憑證生命週期與背景 runtime 拆分落地</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>3.6.5</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>M3.6</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Service principal／credential lifecycle：hash、scope、expiry、rotation、revoke、audit；遷移共用 X-Internal-Token</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>🟨 code ready／待 production gate</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>ADR-036；ADR-040／ADR-041（OD-001／004 已 closed）</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr"/>
+      <c r="K8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10 ~ 2026-08-16</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>M2 SIT+UAT 通過；憑證生命週期與背景 runtime 拆分落地</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>3.6.6</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>M3.6</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Background runtime 拆分：job registry、worker entrypoint、Cloud Scheduler/Run Job pilot、outbox metrics</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>🟨 pilot ready／待 GCP 演練</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>ADR-037；GCP IAM/Scheduler</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-23</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Kafka 事件骨幹上線；License → provisioning 自動化；promotion 流程定版</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Kafka 事件骨幹：commission.accrued / 工單投影事件上線（替換 outbox 輪詢）</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=In Pr</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>階段閘</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-23</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Kafka 事件骨幹上線；License → provisioning 自動化；promotion 流程定版</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>3.3.1</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>License → provisioning 自動化（開站流程腳本化）</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>⬜〔標注 2026-07-28：ADR-042 生效後，開站不再需要為 refi</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-17 ~ 2026-08-23</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Kafka 事件骨幹上線；License → provisioning 自動化；promotion 流程定版</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>3.6.7</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>M3.6</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>GCP staging→production promotion、GitHub Environments、WIF 隔離、release manifest、rollback/restore evidence</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>🟨 workflow ready／待外部環境</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>ADR-038；3.6.4；3.6.6</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>投影、對帳、intake 契約與第 2 品牌開站演練，M3 收斂</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>技師工作台改吃 CQRS 投影（跨品牌工單聚合）</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⬜〔標注 2026-07-28：ADR-043 已定版師傅專屬 channel </t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>3.1.1 / 2.4.1</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>投影、對帳、intake 契約與第 2 品牌開站演練，M3 收斂</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>3.2.1</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>期末對帳 reconcile 閘門（品牌計費 vs 平台結算對平）</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=In Pr</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="8" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>投影、對帳、intake 契約與第 2 品牌開站演練，M3 收斂</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>3.2.2</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>refinery intake 改走受控 API（ADR-042）：intake 端點 + DTO 資料最小化 + cursor/增量水位 + 逐租戶用量計量；REFINERY_POSTGRES_URI 直讀加 usage counter 後退場</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>ADR-042；ADR-036/040 憑證</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>投影、對帳、intake 契約與第 2 品牌開站演練，M3 收斂</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>3.4.1</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>雲端拓撲對齊（tech / platform 面雲端部署 + 技師庫上雲）</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=Done—</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>2.4.1</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="8" t="inlineStr"/>
+      <c r="K16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24 ~ 2026-08-31</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>投影、對帳、intake 契約與第 2 品牌開站演練，M3 收斂</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>3.5.1</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>第 2 品牌租戶開站演練（全流程 dry-run：申請 → 核准 → 開站 → 綁 LINE）</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>3.3.1</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>🛑 不排進衝刺 —— 待裁決，裁決下來才插隊</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>待裁決</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>混合派工（指派為主、搶單為輔）卡在 CR-0191 §8 的六項業主裁決。 沒裁決不能開工——搶單那一半是從零開始（現行只有候選 GIS 與評分排序， 師傅端無 accept/reject、offer 概念不存在），估不出工期也定不了驗收條件。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>3.1.3</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>混合派工：指派為主、搶單為輔（指定師傅逾時未接 → 釋出公開池）。現行為純指派制，offer／accept／搶單併發控制全部不存在</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>🛑 待裁決</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>業主完成 CR-0191 §8 六項裁決後插入最近一個衝刺</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>⬜ 明確排除 —— M4：M4 平台化地基屬階段二（flow DSL 引擎、兩層渲染、Vertical Pack、積木庫、 FlowEditor、AI Onboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>flow DSL 引擎產品化</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>兩層渲染</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr"/>
+      <c r="J22" s="8" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Vertical Pack 打包</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>積木庫 bootstrap</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>FlowEditor 拖拉</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>AI Onboarding Compiler</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>不在本期範圍</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>刻意寫成一條宣告而不是「先不管它」——不指名的話，8 月底沒做完會被讀成滑期， 而它從一開始就不在範圍內。範圍砍掉是決定，不是失敗。</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>第 2 產業落地</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K27"/>
+  <mergeCells count="2">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A20:K20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 里程碑與已定案決策" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,17 +67,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,20 +118,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -641,81 +641,93 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  本專案目前沒有 Cycle</t>
+          <t xml:space="preserve">  Cycle（sprint 容器）</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Plane 的 Cycle 是迭代時間盒。本專案的排程只到 Milestone 層，尚未建任何 cycle；在那之前「這個 sprint 交付什麼」這個問題沒有載體。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="1" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr"/>
+          <t>Plane 的 Cycle 是迭代時間盒。2026-08-05 起由 _plane/import_spine.py 建 Sprint 01–06（各 2 週、連續不重疊、冪等）——在那之前全庫 cycle 出現 0 次，「這個 sprint 交付什麼」這個問題根本沒有載體。⚠️ 但**不自動把需求塞進 cycle**：排程是 PM 的決策，agent 只建容器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 的 V14 是什麼</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>那條 FR 在 Plane 的拆解樹上沒有 parent：它有多條 essential 邊（服務多條旅程），或只有 supporting 邊，且未宣告 scope: global，所以推不出唯一的 parent 旅程。它是 finding 不是 error——擋生成只會逼人亂挑一條。要關掉它，由 BA 在 _relations/sc_requires_rq.yaml 對應的 essential 邊加 primary: true。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>黃色欄位</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
-        </is>
-      </c>
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>灰色欄位</t>
+          <t>黃色欄位</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+          <t>只有人能填。系統不會、也不該幫你填。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>灰色欄位</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>白色欄位</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>正典敘述，同樣改上游。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>四個狀態軸不得互推</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
-        </is>
-      </c>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>四個狀態軸不得互推</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
@@ -732,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -805,220 +817,1582 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>FR-AGT-01</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-01、SC-02）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-02、SC-17</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="inlineStr"/>
+      <c r="J2" s="7" t="inlineStr"/>
+      <c r="K2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FR-AGT-03</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-01、SC-02）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-02</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>FR-AGT-05</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——3 條 essential 邊（SC-02、SC-03、SC-10）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>SC-02、SC-03、SC-10</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>FR-AGT-06</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-01、SC-02、SC-19），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-02、SC-19</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>FR-AGT-10</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-01），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-02</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-04、SC-07）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SC-04、SC-07</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-03</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-04、SC-07）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SC-04、SC-07、SC-08</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-04</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-03、SC-04）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>SC-03、SC-04</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-05</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-05、SC-14）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>SC-05、SC-14</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-06</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-05），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-08</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-06、SC-07）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>SC-06、SC-07</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-11</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-08、SC-09）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SC-06、SC-08、SC-09</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-12</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-09、SC-13）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>SC-09、SC-13</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-13</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-02、SC-10）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>SC-02、SC-10</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-14</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-05），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-17</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-04），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FR-API-18</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-08、SC-11）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>SC-07、SC-08、SC-11</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>FR-DAT-04</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-01、SC-15），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>SC-01、SC-15</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>FR-PLT-01</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-12、SC-17）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-17</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>FR-PLT-02</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-11、SC-18）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>SC-11、SC-16、SC-18</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>FR-PLT-04</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-13、SC-14），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>SC-13、SC-14</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="K22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>FR-PLT-05</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-18），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>FR-PLT-09</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-12、SC-17）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-14、SC-17</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FR-REF-03</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-15、SC-16）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>SC-15、SC-16</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>FR-REF-04</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-15、SC-16）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>SC-15、SC-16</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>FR-TEC-02</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-12、SC-14）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-14</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>FR-TEC-03</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-05、SC-14）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>SC-05、SC-12、SC-14</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>FR-TEC-04</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-05、SC-06）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>SC-05、SC-06</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>FR-TEC-06</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-09、SC-13）分不出主旅程，請於其中一條標 primary: true</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>SC-09、SC-13</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>FR-WEB-01</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-12、SC-17），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-17</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FR-WEB-04</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-08、SC-09），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>SC-08、SC-09</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上沒有 parent——待 BA 宣告 primary</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>FR-WEB-05</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-11、SC-18、SC-19），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>SC-11、SC-18、SC-19</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
           <t>OD —— 開放架構決策（14_ADR/open_decisions.yaml；不是已定案 ADR）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>開放架構決策（ADR 實作細節）</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>OD-001 OHS 服務間憑證模式</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>品牌 API 呼叫技師共享池 OHS 時，定版 OIDC client-credentials 或 internal token，並定義 audience、scope、輪替、撤銷與跨品牌權限邊界。
 Gate: 在 OHS 成為 production 派工唯一依賴、或第 2 個品牌接入前，必須定版並完成負向契約測試。</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-12、SC-14</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>開放架構決策（ADR 實作細節）</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>OD-002 knowledge-refinery 的資料進入契約</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>定版 Refinery 取得診斷對話、問題卡與素材的權威入口：受控 API、批次匯出/唯讀 DB，或 Kafka/outbox event；並定義補數、重播、tenant scope、PII 最小化與 provenance。
 Gate: 在把 Refinery 標為 License 可售附加服務、或允許自動排程 intake 前，必須選定一條主入口及其回補規則。</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>SC-01、SC-02、SC-15、SC-16</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>開放架構決策（ADR 實作細節）</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>OD-003 技師即時 WebSocket 的權威歸屬</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>定版技師工作台的即時事件由 brand API、technician-platform，或雙層 gateway 哪一方擁有；同時定義 channel 授權、事件 owner、replay、Redis/Kafka 依賴與切換策略。
 Gate: 在把 API max instances 調高、或宣稱跨 instance 的技師即時派工 SLA 前，必須定版並完成兩實例與斷線復原 SIT。</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>SC-05、SC-06、SC-12、SC-14</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>OD</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>開放架構決策（ADR 實作細節）</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>OD-004 Casdoor 跨租戶 organization 與 claim 模型</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>在「brand org = 租戶」既有方向下，定版跨品牌技師、platform operator、品牌管理員的 organization membership、role/portal/tenant claims、委派管理與撤銷傳播模型。
 Gate: 在 Casdoor 成為所有 portal 的唯一登入、或首個跨品牌技師/平台治理 production rollout 前，必須定版。</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>SC-11、SC-12、SC-14、SC-17</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>PM + 平台架構師</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
       </c>
     </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>開放架構決策（ADR 實作細節）</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>OD-005 未完成身分驗證的技師施工之責任、保險與揭露義務</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>平台在「技師未完成 KYC 身分驗證即到府施工」的情境下，對客戶的責任歸屬、保險覆蓋、賠償上限與揭露義務為何；以及條件式核准是否需設補件期限與逾期處置。
+Gate: 在對外宣稱技師已完成身分查核之前，或條件式核准累計超過可控件數之前，必須定版。 特別注意 AI 客服的產品知識庫已對客戶明文宣稱「警政單位核發良民證核可」 （agent/lockcore/skills/locksmith-product-knowledge/references/_common/store-info.md:44， 來源為公司官網 bronze 語料）——該聲明對「公司自有鎖匠」可能為真，但對平台 onboard 的師傅目前無任何流程保證。</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>SC-12、SC-14</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>PM + 平台營運負責人</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>PM + 平台營運負責人</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K39"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A34:K34"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Open/In Review/Decided/Superseded/Accepted Risk/Scheduled/Closed" type="list">
+    <dataValidation sqref="K2:K39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 Open/In Review/Decided/Superseded/Accepted Risk/Scheduled/Closed" type="list">
       <formula1>"Open,In Review,Decided,Superseded,Accepted Risk,Scheduled,Closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1082,3166 +2456,3166 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>WBS 工作包（Plane 的 Task 層）—— 27_Product_Roadmap_WBS.md</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0130 R1+R2：死角色全面移除＋86 端點守衛落地＋技師白名單；殘餘 7＝定案保留【自身通知/客戶綁定】）</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>RBAC 轉 enforce：195 條 role_required 對帳 + 逐端點落地（先金流 / 派工）</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SA-01；未授權角色寫入 403（TC 權限類全綠）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0127）</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>角色收斂：_STAFF_ROLES 4 值、rolePolicy 移除死角色、_MATRIX 補 operations_manager 行、Schema 註解同步</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SA-06；13_Security §3.1 正典一致</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0131：金流/派工終局 20 端點 fail-closed＋surface 剔除測試 6 項）</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>fail-closed 白名單 + API_SURFACE 剔除清單測試</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SA-03 / SA-05</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0128）</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>工單狀態機對齊「報價先行＋現場修正輪」（flow gate + 轉移表）</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>02_BRD §5.7；TC-WO-*、TC-ONSITE-07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0129；加價額 1500 已定案）</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>急件事後補審引擎（timer + 補審佇列 + 事後 LIFF/紙本 + 逾時升級）</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>FR-API-19；15_SDS §4.5；TC-DISPATCH-08；急件加價額 1500 已定案（CR-0129 D1a）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0132 schema/引擎）＋2026-07-10（CR-0138 前端 UI：診斷雙 gate 編輯 modal＋待補知識佇列頁；Gate① enforce 現可開啟）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>問題卡雙 gate schema（CIA + migration：雙完整度 / 分流欄 / RMA spine / knowledge_ready / tenant_id）</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>BE+DT</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>CIA 裁決</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>15_SDS §4.6；18_DB §4.3 目標欄位</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>1.2.4</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0133：三方存檔驗證測試＋失敗 ERROR 告警＋spool 補送零缺漏）</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>對話三方全量存檔驗證（接管期間零缺漏 + 寫入失敗告警）</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>AG+BE</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>FR-A11 / BR-CONV-03；FR-AGT-09 驗收</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>1.3.1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0134：Redis 橋 opt-in＋PG advisory 領導者選舉掛滿 11 worker；多實例 e2e 已落 CI 2026-07-10 CR-0151——雙實例共 Redis 跨實例廣播實證＋負向對照；部署面掛 REDIS_URL 仍=OPS）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>即時通道：WS hub 遷 Redis pub-sub + cron 分散式鎖</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>BE+OPS</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>SA-02；多實例不遺失、cron 不重跑</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>1.4.1</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>🔶 code 面 ✅（CR-0136 api＋CR-0156 agent/refinery/web-參考實作＋agent OPIK 接線＋PII scrub 全面，2026-07-10）；殘＝SigNoz 叢集部署與 OPIK/OTLP secrets 配置（OPS）＋三站複製〔標注 2026-07-22：三站複製完成——tech-portal/landing/platform-console 各補 instrumentation.ts（OTLP opt-in no-op 範式同 brand-portal）＋@vercel/otel＋vitest 單元測試 6×3 綠（feat/otel-three-portals）；code 面殘項歸零，僅剩 SigNoz 部署＋secrets 配置（純 OPS）〕〔標注 2026-07-22（業主裁決）：維持 🔶／In Progress，SigNoz 部署綁「真實營運開始」——SigNoz 為常駐基礎設施（ClickHouse ~$50-100/月+維運），非一次性配置；單品牌尚無真實流量，現在部署無數據可看。解除條件＝營運流量開始後部署 SigNoz 叢集+設 OTEL_EXPORTER_OTLP_ENDPOINT。In Progress 誠實反映「code 完成、後端未部署」，非停滯。全 In Progress 解除條件盤點＝docs/audit/inprogress-exit-criteria-20260722.md〕</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>可觀測性：SigNoz（metrics/logs/traces/alerts）+ OPIK（LLM 品質）基線</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>OPS+AG</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>ADR-007；25_Monitoring_Spec</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>1.5.1</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0135：200 題 corpus＋judge 七分類＋dry/live gate runner＋CI；live 全量 nightly workflow 已掛 2026-07-10——GEMINI_API_KEY secret 未配置時 nightly 亮紅提示，OPS/1.6.1 配置後自動生效）</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>AI 禁區 200 題 Eval pipeline 常態化（每 deploy 跑，&lt;95% block）</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>FR-A10 / K8</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>1.6.1</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>🔶 drift-check ✅ 2026-07-09（CR-0136：migration 檔案層守門 CI＋12 支波次補登；Cloud Run CD 觸發器＝OPS）〔標注 2026-07-27：再增兩道 CI gate——①web-lint-typecheck.yml（四站 matrix tsc+eslint；補前發現四站 npm run lint 因無 ESLint 設定與依賴而從未運作過）②scripts/ci/endpoint-guard-audit.py（端點守衛不對稱雙檢：v2/legacy 孿生＋list/detail），已反向驗證有效（修復前抓 8 組、修復後清零）〕</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>基礎 CD：3 Cloud Run 自動部署 + migration drift-check CI</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>ADR-P012（G-12 / G-10）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>1.7.1</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0137：api 1719 passed 全綠＋修 seed 順序 bug/測試污染/legacy 斷言；1 live 測試 Vertex 429 非迴歸）〔標注 2026-07-27：全套回歸能力解封——新增 scripts/db/make-test-db.sh（pg_dump 複製 UAT 庫＋補套 migration 建隔離 scratch 庫），此前因 pytest 單庫 fallback 直打 5433 UAT 庫而無法安全跑全套。實測 api 2091 passed / 13 failed（13 支 seed 依賴非回歸）＋agent 309 passed；並據此確認本輪 20 個端點角色守衛變更零回歸〕</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>SIT：M1 範圍 TC 全綠 + 回歸</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1.1–1.6</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>SIT 報告</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>M1 上線硬化（單品牌可收費上線）</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>1.7.2</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-22（業主裁決完成判準改制：功能完成＋代理 UAT＝完成，親驗移交外部測試人員。收案依據：三輪代理 UAT 112 findings 全數收斂＋合約紅線 eval 實測 K8 98.5%/K3' 100%/紅線 9/9＋0719 上雲 C 系列修復輪。外部驗證依 UAT-M1M2-acceptance-checklist，發現以新 finding 開卡不重開 gate）</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>UAT：合約紅線（K1 ≥ 80% / K3 ≥ 95% / K8 ≥ 95%）+ 業主驗收</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>QA+PM</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1.7.1</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>22_UAT 報告；M1 Release gate</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>2.1.1</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>🔶 R1 ✅ 2026-07-10（CR-0141：Casdoor 部署 profile idp＋org/角色/users bcrypt 遷移同步＋api OIDC 雙驗 opt-in＋cookie 地基；live E2E 實證；api 1729 綠。R2 ✅ 2026-07-10（CR-0146：授權碼流 brand-portal 參考實作＋httpOnly cookie 雙寫，live E2E 全通）。R3 待做：ACT-01 localStorage 退場（30+ 頁同步改造）＋三站複製接線——業主排程；License gate 依 ADR-004 隨 ADR-002）</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Casdoor 統一 IdP：org（租戶）/ OIDC 授權碼流 / License 訂閱管理</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>BE+OPS</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>ADR-004（Casdoor）；web token 改 httpOnly（ACT-01）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>2.1.2</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-10（CR-0143：申請/審核/直建早已落地（088/CR-0114 R5）；本輪補 SoD 雙簽生產接線——4 端點＋UI（同人核准 403），13_Security §3.1 銷案。api 1733 綠）</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>租戶自助開帳：員工申請 tab + Admin 審核指派（4 角色）+ SoD 雙簽</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>FE+BE</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2.1.1</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>13_Security §3.1 開通權矩陣</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>2.2.1</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-09（CR-0124/0125，提前於 M1 期完成）</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>RAG 語義層：embed() + pgvector 語料 + MCP server</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>AG+DT</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>agent ADR-004；FR-A03 / FR-AGT-07</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>2.2.2</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-10（CR-0142 收案：驗收依 ADR-030 重定義——語料灌注 ✅＋引用率轉輔助品質指標（live 基準 83%）＋Skill 重切取消。同輪修撞名事故：RAG 主表原名撞 kb manual_chunks 恆 no-op → 096 改名 rag_manual_chunks 自持，UAT live 灌注 249 chunk 首次真正可檢索）</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>語料灌注：型號事實 chunk 遷移 + Skill 重切（行為留 skill、事實入 RAG）</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2.2.1</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>ADR-030 重定義：語料灌注＋引用率輔助指標（原 ≥90% cutover gate 取消）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>2.3.1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-10（CR-0139：refinery/ member——DB 直連汲取 default-deny＋LLM 兩軌分流＋migration 094 Draft Queue 狀態機；7 tests；live LLM 煉製隨 2.3.2 驗。case_entries 表名衝突落 §8-1 待業主，阻 2.3.2）〔標注 2026-07-11：CR-0157 目錄遷至 knowledge-pipeline/refinery/〕</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>knowledge-refinery 服務：診斷對話輸入汲取（吃 knowledge_ready 卡）+ 提煉分流</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1.2.3 / 1.2.4</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>ADR-018；KR P1/05（已整併 15_SDS §9）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>2.3.2</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-10（CR-0140：case_entries 併形 095＋rag 案例查詢修復；FastAPI 審核服務＋UI :8002；Publisher 核可才落地——事實軌 embed+case_entries／行為軌 patch+apply CLI；12 tests。遺留：auth 隨 2.1.1 Casdoor 化）</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>HITL 審核 UI（draft → 人審 diff → 核可落地 pgvector + skill）</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>FE+DT</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2.3.1</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>ADR-018 §審核層</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>2.3.3</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-13（CR-0167/0168 LiveSkill：skill 從綁 image 改「品牌庫 SSOT＋agent workspace overlay 物化」，發佈後 ≤60s 生效不重佈——migration 106 版控（saas.skill_revision/skill_bundle/skill_audit_log）＋skills_v2 API（CRUD/publish/回滾）＋SkillSync 60s 輪詢物化＋品牌後台「AI 技能」編輯/版本/發佈/回滾＋refinery 行為軌改走 /internal/skills/ingest（merge draft 人審發佈）；品質保證回歸測試位元組級不變；api 14＋agent 9＋refinery 7 綠。剩 agent 重佈一次由使用者執行）〔標注 2026-07-13（CR-0167）：本列 LiveSkill 為業主 CR-0167 新能力，原 roadmap 知識線無對應項，依「新增段」補登〕〔標注 2026-07-18：三項追加——①容器缺口修復（compose 缺 AGENT_TENANT_ID＋agent image 缺 psycopg，LiveSkill 在容器從未生效，fail-soft 掩蓋；已修＋雲端重佈 checklist 記載）；②rel_path 驗證閘 ASCII 白名單擋出廠中文/括號/加號實檔→品牌後台對產品知識庫存草稿/發佈全 422 死鎖（seed 直 SQL 繞過入庫暗藏），改黑名單制＋回歸測試 2（CR-0167 進度）；③#10 知識庫 UI 三步完結（CR-0171：口語化＋品牌分組收合樹＋型號知識新增精靈——小編表單新增不寫 markdown，存草稿 live 實證含中文檔名整樹 PUT）〕</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Skill 熱更新 LiveSkill：知識版控 + 品牌自維編輯 + pipeline 自動汲取 draft + 熱物化不重佈</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>BE+AG+FE</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2.3.2</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>ADR-032；CLAUDE.md Arch Lock 條 2</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>2.4.1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>🔶 方案A/B 已落地（CR-0112：雙 stack＋技師身分權威庫拆分＋投影雙寫＋API_SURFACE 塑形＋tech web；稽核 2026-07-10 查實）。ADR-016 完整形態（OHS API/事件投影/品牌不直連）依業主 0703 裁決隨 AI-2/AI-3〔標注 2026-07-22（Plane 對帳輪）：Plane 卡已改 Done——0719 tech/platform 上雲＋B1 業主親證（0721 codegraph 稽核輪改卡）；殘項 ADR-016 完整形態本屬階段二 AI-2/AI-3 範圍，階段一範圍已完。原文 🔶 不動，狀態升 ✅ 留待業主確認〕</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>technician-platform 獨立系統：技師庫 + tech-api + 師傅 web 拆出</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>ADR-016；跨租戶單一身分</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>✅ 2026-07-10 帳面收斂（CR-0115 早已落地：migration 089/090＋三層註冊＋PII 加密＋文件上傳＋平台審核 KYC 區塊＋測試 14+；稽核查實。遺留：雲端套 089/090＋GCS 落點＋tech-register i18n）</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>✅ 2026-07-10 帳面收斂（CR-0115 早已落地：migration 089/090＋三層註冊＋PII 加密＋文件上傳＋平台審核 KYC 區塊＋測試 14+；稽核查實。遺留：雲端套 089/090＋GCS 落點＋tech-register i18n）＋2026-07-30 CR-0195 條件式核准（核准端原本對文件零檢查、核准後補件被封死；現改為文件不齊須顯式條件式核准並落稽核事件＋補件通道放寬至 active＋清單「文件未齊」可視性＋migration 126。責任側空白見 OD-005。prod 未部署）</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>技師 KYC 註冊三層（登入/註冊分離 + 敏感 PII + 文件上傳）</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2.4.1</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>CR-0115（七項設計裁決依 §8）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>2.4.3</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-10（CR-0144：/internal/requote-requests＋冪等回放/409＋v+1 supersedes 串鏈＋cs_fallback 降級＋TC-DISPATCH-07 測試 4/4。技師 UI 入口＋cs_fallback 代發起已補（scope-change 舊頁原地改造去定價）；多品牌路由隨 AI-2/AI-3）</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>OHS requote command 通道（tenant 路由 + 冪等 + 降級）</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2.4.1 / 1.2.1</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>ADR-027；FR-TEC-07；TC-DISPATCH-07</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>2.4.4</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-17（CR-0169 技師 LINE 推播全鏈：綁定碼＋webhook HMAC 驗簽＋推播服務（內容最小化無 PII）＋assign/reassign/池單三掛點＋師傅站綁定卡；live E2E＋pytest 6 綠。剩外部：業主送件平台 LINE 官方帳號（Messaging＋Login 兩 channel），憑證到手帶 env 重佈即生效）＋（#18 首步：師傅站 PWA 可安裝化——manifest/SW 離線殼/install 橫幅/iOS 手動加入；Playwright 驗證 beforeinstallprompt 可安裝；完整 RN 為月級終態待商業決策）〔標注 2026-07-18：本列為 0715 會議 #14/#18 技師觸達訴求，原 roadmap 無對應項，依「新增段」慣例補登（同 2.3.3 先例）〕</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>技師觸達：平台 LINE 官方號推播（接單即知）＋師傅站 PWA（裝主畫面、全螢幕）；RN APP 為後續終態</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2.4.1</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>CR-0169；0715 會議 §七</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>2.5.1</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>🔶 Gate-1 凍結 enforced 2026-07-10（CR-0145：baseline 195 ops＋CI 守門——新增 v1 即紅）。遷移/移除受三項業主待決阻擋（auth 定位/platform v2/5-gate 名實，CR-0145 §8），依 ADR-003 排 M3〔標注 2026-07-20（codegraph 盤點，不改原文）：v1→v2 遷移就緒盤點完成（61-agent codegraph workflow）——25 router／101 端點，對抗驗證 39 CONFIRMED 可移除、43 REFUTED（全數卡 pytest/CI/deprecation 契約測試，非前端流量）、4 真前端阻擋（media/reconciliations）、15 keep；work_orders 11 端點屬 onsite/LINE 高爆炸半徑，須逐一 CIA + 人工複查（不得列低風險波次）。低風險 Wave1 整檔可清＝dashboard/inventory/resolution/disputes/settlements。報告＝.claude/context/quality/codegraph-v1v2-migration-audit-2026-07-20.md。本盤點為 2.5.1 遷移 prep，🔶 狀態不變（移除/遷移仍受業主 §8 三項待決阻擋）。〕</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>v1 API 收斂：凍結 → 遷移 ~42 caller → 移除（5-gate）</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>ADR-P012（G-09）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>M2 身分・知識・技師平台（三線平行）</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>2.6.1</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>🔶 SIT ✅ 2026-07-10（CR-0147：api 1738＋agent 162＋rag 7（含新 MCP 整合）＋refinery 12 全綠；五項 live 實證含 refinery 真 LLM 煉製與 OIDC 瀏覽器全流程）。UAT=業主（M1 1.7.2＋M2 驗收，合約紅線 K1/K3/K8）〔標注 2026-07-18：功能面 UAT 前置已由兩輪大範圍代理 UAT 收斂——業主指示代理實測（第一輪 5 角色四站 39 findings＋第二輪六功能域 43 findings，共 82 項）→ 修復/裁決全數處置（api 全套 1931 綠、四站 tsc 0；報告 docs/uat/uat-full-report-20260718.md＋uat-round2-report-20260718.md）。本列 UAT gate 本體（業主親驗＋合約紅線 K1/K3/K8 live）仍待業主執行，不因代理 UAT 視為通過〕〔標注 2026-07-22：✅ 收案——業主裁決完成判準改制（功能完成＋代理 UAT＝完成，親驗移交外部測試人員）；收案依據＝SIT 全綠＋三輪代理 UAT 112 findings＋雲端 B1/B2 實證；LiveSkill 親驗版一併移交外部測試。前段 0718 標注之「不因代理 UAT 視為通過」自此依新判準失效〕</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>M2 SIT + UAT（含跨系統整合場景）</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2.1–2.5</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>M2 Release gate = 階段一完成</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=In Progress——0721 codegraph 稽核證事件骨幹 code 已在，惟 opt-in KAFKA_BOOTSTRAP 未啟用=runtime 休眠；非未動工亦非完成〕</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Kafka 事件骨幹：commission.accrued / 工單投影事件上線（替換 outbox 輪詢）</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>BE+OPS</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>階段閘</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>ADR-006 / ADR-017；17_AsyncAPI</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>⬜〔標注 2026-07-28：ADR-043 已定版師傅專屬 channel 由 technician-platform 持有，本列的「跨品牌聚合」自此有明確 owner；遷移仍待 Redis／Kafka 取證〕</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>技師工作台改吃 CQRS 投影（跨品牌工單聚合）</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>BE+FE</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>3.1.1 / 2.4.1</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>FR-TEC-*；TC-DISPATCH-05 欄位最小化；ADR-043</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>🛑 待裁決</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>混合派工：指派為主、搶單為輔（指定師傅逾時未接 → 釋出公開池）。現行為純指派制，offer／accept／搶單併發控制全部不存在</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>PM+BE+FE+QA</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>CR-0191 §8 六項業主裁決；3.1.1；ADR-043</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>CIA＝docs/4-exploration/CR-0191-hybrid-dispatch-assign-then-open-pool.md；併發承接「N 搶 1 恰好一成功」測試為硬門檻</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>3.2.1</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=In Progress——0721 codegraph 稽核證 reconcile 閘門雛形 code 已在，生產未啟用〕</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>期末對帳 reconcile 閘門（品牌計費 vs 平台結算對平）</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>BE+DT</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>BR-SETTLE-05；FR-E03</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>refinery intake 改走受控 API（ADR-042）：intake 端點 + DTO 資料最小化 + cursor/增量水位 + 逐租戶用量計量；REFINERY_POSTGRES_URI 直讀加 usage counter 後退場</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>BE+DT</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>ADR-042；ADR-036/040 憑證</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>收費服務前置：逐租戶計量可出帳；直讀使用量連續一個 release window = 0</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>⬜〔標注 2026-07-28：ADR-042 生效後，開站不再需要為 refinery 額外配 DB 憑證與網路路徑——本列的 provisioning 腳本應以 service principal 取代之〕</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>License → provisioning 自動化（開站流程腳本化）</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2.1.1</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>ADR-002（per-brand bundle）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>3.4.1</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>⬜〔標注 2026-07-22（Plane 對帳輪）：Plane 卡=Done——0719 tech/platform 面雲端部署＋技師庫上雲，B1 業主親證（0721 稽核輪改卡）；本列經業主確認後可打 ✅〕</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>雲端拓撲對齊（tech / platform 面雲端部署 + 技師庫上雲）</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2.4.1</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>平台 L1 G-01 收斂</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>M3 多品牌規模化（業主裁決 2026-07-07：自階段一移入階段二）</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>3.5.1</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>第 2 品牌租戶開站演練（全流程 dry-run：申請 → 核准 → 開站 → 綁 LINE）</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>PM+OPS</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>開站 SOP 文件化；M3 Release gate</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>3.6.1</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-27</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>前端 mutation contract：optimistic／server-confirmed 分級、rollback、精準 invalidation、action idempotency、409 conflict UX</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>FE+BE+QA</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>ADR-034</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>shared-contract/mutation + Notification reference；offline/retry、5xx、409 Playwright 3/3，同 action key 重送與 rollback 已證</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>3.6.2</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-27（HTTP；跨 host realtime 另受網域 gate）</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>偏好與登入資料分層：三庫 user_preferences allowlist、跨裝置同步；localStorage token 退場</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>FE+BE+DT</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>ADR-034；2.1.1；OD-004 已 closed（ADR-041：單一平台 principal + 品牌 membership）</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>migration 120 二套；三面 API/CAS/16 KiB tests；四站 same-origin proxy + HttpOnly cookie；browser token scanner 通過</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>3.6.3</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-27</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Brand Portal Capability-driven Command Palette v1</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>FE+BE</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>3.6.2；ADR-034</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Ctrl/⌘+K；搜尋／草稿／佇列／通知／saved view；capability + rolePolicy 雙過濾，unit/build 通過</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>3.6.4</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-27</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>API resource ownership matrix 與 BOLA／IDOR parameterized contract tests</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>SEC+BE+QA</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>ADR-035</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>runtime mutation + sensitive read/export 100% 分類；六類 contract 皆綁 real negative test node id，CI completeness 通過</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>3.6.5</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>🟨 code ready／待 production gate</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Service principal／credential lifecycle：hash、scope、expiry、rotation、revoke、audit；遷移共用 X-Internal-Token</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Platform+SEC+BE</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>ADR-036；ADR-040／ADR-041（OD-001／004 已 closed）</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>migration 121、API/auth/caller/負測已綠；transport/claim 已定案（ADR-040／041）；尚缺 principal/secret bootstrap 與 fallback usage 連續一個 release window = 0</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>3.6.6</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>🟨 pilot ready／待 GCP 演練</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Background runtime 拆分：job registry、worker entrypoint、Cloud Scheduler/Run Job pilot、outbox metrics</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>BE+OPS</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>ADR-037；GCP IAM/Scheduler</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>14-job registry、獨立 entrypoint、hybrid cutover flag、六項 SLI、Cloud Run Job 腳本已綠；尚缺真實 shadow→cutover→rollback／重跑證據</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>3.6.7</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>🟨 workflow ready／待外部環境</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>GCP staging→production promotion、GitHub Environments、WIF 隔離、release manifest、rollback/restore evidence</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>OPS+QA+SEC</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>ADR-038；3.6.4；3.6.6</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>同 digest workflow、雙環境 manifest、health/smoke、rollback/drill tooling 已綠；2026-07-27 稽核 repo Environments=0、Actions vars/secrets=0，且私有 repo 目前方案拒絕 branch protection／required reviewer（403）；尚缺 WIF 與 rollback/forward-fix/restore 真實演練</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>M3.6 Plane 借鏡架構優化（跨產品體驗、安全與交付）</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>3.6.8</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>✅ 2026-07-27</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>web/shared-contract 版本化窄例外：runtime types、RFC7807、mutation/conflict、capability contract</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>FE+OPS</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>ADR-039；3.6.1；ADR-031 runtime export</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>0.1.0 immutable vendored tarball；boundary/test/build、consumer matrix、四站 lockfile/tsc/production build 全綠；Next/PostCSS/sharp/brace-expansion 修補後完整 audit 皆 0 vulnerability</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>flow DSL 引擎產品化</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>從鎖匠 pack 抽出引擎（DSL-first 鐵律：引擎先於 UI）；積木契約 + 匯入靜態驗證 / ADR-013；15_SDS §3.3-3.5</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>兩層渲染</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>field_metadata 配置驅動（DynamicForm/Table）+ ui_composition 元件組裝；現行鎖匠前端漸進遷移，不 big-bang 重寫 / ADR-001；07_workorder §8.1</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Vertical Pack 打包</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>pack@version + 租戶覆寫 + 向後相容檢查；鎖匠版收斂為第一個正式 pack / 07_workorder §4</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>積木庫 bootstrap</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>頭 2-3 產業積木手工建（誠實面對冷啟動） / ADR-014 鐵律 2</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>FlowEditor 拖拉</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>薄編輯器，只產出/編修 DSL / FR-F07</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>AI Onboarding Compiler</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>SOP/訪談 → Block Ontology → draft DSL → HITL 人審（金流/派工/同意書必過人審）；與 knowledge-refinery 共用審核 UI 骨架 / ADR-014 / FR-F08</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>M4 / M5 平台化（概要層級）</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>第 2 產業落地</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>FDE 4 配置面走通（診斷 / 知識精煉 / flow / UI 組裝），驗證飛輪 / 07_workorder §8.2</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>ADR —— 14_ADR/00_INDEX.md（append-only，不改舊內容）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>ADR-001</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>平台核心 vs 領域配置分層（TRIZ 按系統層級分離）</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>009 · 013 · 014 · 002</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>ADR-002</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>per-brand 授權部署（大單體 + 內部容器 + 集中共用元件）</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>004 · 016 · 020 · 006</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>群 A — 平台奠基與部署</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>ADR-003</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>排程中</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>平台工程治理排程（migration 防漂移・API 收斂・CD）</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>002 · 021 · 022</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>群 B — 身分與授權</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>ADR-004</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Casdoor 統一 IdP + 租戶 + License 授權</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>005 · 002 · 024</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>群 B — 身分與授權</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>ADR-005</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>四方 RBAC 模型 + enforce（deny-by-default）</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>004 · 016 · 022</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>群 C — 即時、事件與可觀測性</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>ADR-006</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>規劃中</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>即時高併發骨幹（Kafka 事件 + Redis fanout + 讀寫分離）</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>002 · 016 · 017 · 007</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>群 C — 即時、事件與可觀測性</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>ADR-007</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>可觀測性分層（SigNoz 系統監控 + OPIK Agent LLM Ops）</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>002 · 009 · 012</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>群 D — Agent 與模型</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>ADR-008</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Agent 核心採 LockCore（fork nanobot 最小核心）</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>系統(agent)</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>009 · 010 · 011 · 025</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>群 D — Agent 與模型</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>ADR-009</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Model Orchestration Layer 供應商無關（LiteLLM 實作）</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>001 · 008 · 010 · 007</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>群 D — Agent 與模型</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>ADR-010</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>知識分層：Skill 行為驅動 + RAG-via-MCP 檢索（從屬非收斂）</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>系統(agent)</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>008 · 011 · 018 · 019 · 012</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>群 D — Agent 與模型</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>ADR-011</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Agent 整合風格三分類（MCP / HTTP-internal / 不暴露）</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>系統(agent)</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>010 · 025 · 015</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>群 D — Agent 與模型</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>ADR-012</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Agent Configuration Studio 品牌自服務調校</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>001 · 010 · 009 · 005 · 018</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>ADR-013</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Accepted（分期）</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Flow-as-Blocks 宣告式 DSL + 配置驅動引擎（DSL-first）</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>001 · 014 · 015</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>ADR-014</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>規劃中（北極星）</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>AI Onboarding Compiler + Block Ontology（護城河）</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>013 · 018 · 001</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>群 E — 工單平台與流程自動化</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>ADR-015</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>工單狀態機核心不變式（locksmith flow 首個實例）</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>系統(api)</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>013 · 025 · 026</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>群 F — 技師平台</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>ADR-016</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>技師共享池獨立系統（跨租戶單一真相）</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>002 · 017 · 006 · 004</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>群 F — 技師平台</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>ADR-017</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>技師平台佣金邊界 + 工單可見性（CQRS 投影）</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>016(refines) · 002 · 006</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>ADR-018</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>知識精煉獨立服務（draft → HITL 審核 → 寫入）</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>010 · 019 · 014 · 004</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>ADR-019</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Medallion 分層數據架構（raw→bronze→silver→refinery）</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>系統(data)</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>018 · 010</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>ADR-020</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>三庫物理隔離的租戶隔離模型</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>系統(data)</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>002 · 016 · 017 · 021</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>群 G — 知識精煉與數據</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>ADR-021</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>psycopg3 raw SQL + 純 SQL forward-only migration</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>系統(api/data)</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>020 · 003</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>ADR-022</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>API_SURFACE 單體多面塑形（一 codebase → 三暴露面）</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>系統(api)</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>005 · 004 · 006 · 002</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>ADR-023</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Superseded by 028</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>單一 codebase 以 APP_MODE build 多 portal</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>系統(web)</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>022 · 024</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>群 H — API 與 Web 形態</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>ADR-024</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>web 為 client SPA（無 BFF）+ Context 狀態 + OIDC 認證</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>系統(web)</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>023 · 004 · 005</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
     </row>
     <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>群 I — 領域安全紅線</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>ADR-025</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>AI 話術邊界與「永不自轉工單」紅線憲章</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>011 · 015 · 012</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>群 I — 領域安全紅線</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>ADR-026</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>報價快照 hash-chain 不可否認性</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>系統(api)</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>015 · 021</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>ADR-027</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>現場報價修正發起邊界——技師平台只發 command、品牌 api 為報價唯一權威</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>016 · 017 · 026</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr"/>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>ADR-028</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>web 檔案層拆分——四站台完全獨立專案（複製分家）</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>系統(web)</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>supersedes 023 · 022 · 024</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr"/>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>ADR-029</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>知識產線雙軌重構——data/ 改名 knowledge-pipeline + facts/behavior 分軌 + provenance 治理</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>系統(knowledge-pipeline)</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>010 · 018 · 019</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr"/>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>ADR-030</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>RAG-MCP＝對外開放介面；Skill 為知識與推理主軸（cutover 取消）</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>部分取代 010 · 011</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
     </row>
     <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>ADR-031</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>契約工件三分層——前端型別 SoT＝runtime export；設計稿 spec 專職設計期契約</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>系統(api/web)</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>refines 022 · 028</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
     </row>
     <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>ADR-032</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Skill 熱更新——品牌庫為 SSOT、image builtin 降級離線保底、workspace overlay 物化（≤60s 生效不重佈）</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>平台</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>延續 030 · 細化 CLAUDE.md Arch Lock 條 2</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr"/>
     </row>
     <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>群 J — 跨系統流程邊界</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>ADR-033</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>轉真人判準——SOP 情境式紅線取代 FR-AGT-03 三輪硬計數（正典讓步；Clarify gate 降為話術原則；transfer 唯一出口不變）</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>系統(agent)</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>025 · 008 · 032</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr"/>
     </row>
     <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>ADR-034</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>已實作</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>前端 Mutation 一致性、偏好分層與 Capability 導覽</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>系統(web/api)</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>refines 024 · 005 · 028</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>ADR-035</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>已實作</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>租戶資源歸屬授權契約與 BOLA／IDOR 守門</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>平台/security</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>refines 005 · 020 · 022</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ADR-036</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>實作完成／待 production 取證（transport 已由 ADR-040 定版；餘 fallback 歸零）</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>機器身分與可撤銷服務憑證</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>平台/security</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>004 · 005 · 035</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
     </row>
     <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>ADR-037</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>Pilot code ready／待 GCP 取證</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>背景工作 Runtime 從 API 生命週期拆分</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>系統(api/ops)</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>refines 006 · 003 · 021</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr"/>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>ADR-038</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Workflow ready／待環境演練</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>GCP 發版 Promotion 與證據關卡</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>平台/delivery</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>refines 003 · 002 · 007</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>ADR-039</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>已實作（vendored 0.1.0）</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>web 共享契約套件——四站獨立專案的窄例外</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>系統(web/tooling)</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>refines 028 · 031 · 034</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr"/>
     </row>
     <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>ADR-040</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Accepted（closes OD-001）</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>OHS 服務間憑證定版為受控 opaque credential</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>平台/security</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>036 · 004 · 035</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr"/>
     </row>
     <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>ADR-041</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>Accepted（closes OD-004）</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>跨品牌技師身分採單一平台 principal + 品牌 membership claim</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>平台/security</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>004 · 005 · 035</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr"/>
     </row>
     <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>ADR-042</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>Accepted（closes OD-002）／intake 端點待實作</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>knowledge-refinery 資料進入契約定版為受控 API</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>平台/data</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>018 · 036 · 040</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr"/>
     </row>
     <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>群 K — 體驗、安全執行與交付治理</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>ADR-043</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Accepted（closes OD-003）／待 Redis/Kafka 取證</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>技師即時 channel 歸屬 technician-platform</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>平台/realtime</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>041 · 006 · 017</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G96"/>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 缺口與決策清單" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 里程碑與已定案決策" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="② 缺口與決策清單" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="③ 里程碑與已定案決策" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$39</definedName>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>✅ 2026-07-22（業主裁決完成判準改制：功能完成＋代理 UAT＝完成，親驗移交外部測試人員。收案依據：三輪代理 UAT 112 findings 全數收斂＋合約紅線 eval 實測 K8 98.5%/K3' 100%/紅線 9/9＋0719 上雲 C 系列修復輪。外部驗證依 UAT-M1M2-acceptance-checklist，發現以新 finding 開卡不重開 gate）</t>
+          <t>✅ 2026-07-22（業主裁決完成判準改制：功能完成＋代理 UAT＝完成，親驗移交外部測試人員。收案依據：三輪代理 UAT 112 findings 全數收斂＋合約紅線 eval 實測 K8 98.5%/K3' 100%/紅線 9/9＋0719 上雲 C 系列修復輪。外部驗證依 UAT-M1M2-acceptance-checklist，發現以新 finding 開卡不重開 gate）〔標注 2026-08-05：外部測試人員首批 finding 已收斂，依既定規則不重開 gate——Luca 於 2026-08-03 對整合測試計畫 130 支 TC 做原始碼靜態走查（正式機當時為帳務封鎖止血而停機，動態 UAT 不可行，靜態走查為替代產出；docs/uat/static-walkthrough-20260803/）。其「不一致 9＋部分實作 85」共 94 支經回程式碼逐支查證（開檔覆核每個 檔案:行號、對「零命中」宣稱以多種命名重跑 grep）後：判定正確 61、判重 11（其實一致，已加判定更正標注、原文未改）、判輕 22、引用有誤 36。CIA 豁免的 8 支已修復上線（含兩支 P0：8c380412 客戶在 LINE 同意報價自 2026-07-21 起全數 TypeError、d0e6c585 兜底話術第二現場致客人 AI 永久靜音）；餘 75 支卡 CIA gate，分流為 CR-0201～CR-0211 十一張，🛑 待業主逐張裁決 §8。其中 TC-PLT-FLOW-01 規模為「極大（功能不存在）」——flow_dsl/block_library/vertical_pack 等六個識別碼全樹零命中，屬規格寫了但未排進開發，非缺陷〕</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_規格統控規劃書.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="② 缺口與決策清單" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="③ 里程碑與已定案決策" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 缺口與決策清單" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 里程碑與已定案決策" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 缺口與決策清單'!$A$1:$K$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 里程碑與已定案決策'!$A$1:$G$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -835,7 +835,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-01、SC-02）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-01、SC-02）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-01、SC-02）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-01、SC-02）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——3 條 essential 邊（SC-02、SC-03、SC-10）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——3 條 essential 邊（SC-02、SC-03、SC-10）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-01、SC-02、SC-19），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-01、SC-02、SC-19），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-01），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-01），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-04、SC-07）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-04、SC-07）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-04、SC-07）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-04、SC-07）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-03、SC-04）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-03、SC-04）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-05、SC-14）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-05、SC-14）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-05），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-05），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-06、SC-07）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-06、SC-07）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-08、SC-09）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-08、SC-09）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-09、SC-13）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-09、SC-13）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-02、SC-10）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-02、SC-10）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-05），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-05），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-04），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-04），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-08、SC-11）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-08、SC-11）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-01、SC-15），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-01、SC-15），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-12、SC-17）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-12、SC-17）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-11、SC-18）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-11、SC-18）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-13、SC-14），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-13、SC-14），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-18），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-18），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-12、SC-17）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-12、SC-17）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-15、SC-16）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-15、SC-16）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-15、SC-16）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-15、SC-16）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-12、SC-14）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-12、SC-14）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-05、SC-14）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-05、SC-14）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-05、SC-06）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-05、SC-06）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——2 條 essential 邊（SC-09、SC-13）分不出主旅程，請於其中一條標 primary: true</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——2 條 essential 邊（SC-09、SC-13）分不出主旅程，要指定就於其中一條標 primary: true</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-12、SC-17），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-12、SC-17），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-08、SC-09），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-08、SC-09），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>拆解樹上會沒有 parent——沒有任何 essential 邊（只有 supporting：SC-11、SC-18、SC-19），要先把某一條升為 essential 才能標 primary，或改宣告 global</t>
+          <t>SC 覆蓋歸屬未裁決（不影響拆解樹 parent）——沒有任何 essential 邊（只有 supporting：SC-11、SC-18、SC-19），要先把某一條升為 essential 才能標 primary</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2406,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5617,8 +5617,41 @@
       </c>
       <c r="G96" s="4" t="inlineStr"/>
     </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>群 K — 體驗、安全執行與交付治理</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>ADR-044</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Accepted（2026-08-08）／Plane 投影未移植</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>拆解樹 Feature 錨點改為業務能力（階層 V3）</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>規格治理</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G96"/>
+  <autoFilter ref="A1:G97"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A53:G53"/>
